--- a/data/Supplementary Data 4.xlsx
+++ b/data/Supplementary Data 4.xlsx
@@ -17,6 +17,7 @@
     <sheet name="1 Bar-dominant" sheetId="7" r:id="rId2"/>
     <sheet name="2 Balanced" sheetId="5" r:id="rId3"/>
     <sheet name="3 Y-dominant" sheetId="6" r:id="rId4"/>
+    <sheet name="Pareto sets" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3872,7 +3873,7 @@
         <v>1.0659000000000001</v>
       </c>
       <c r="G2" s="3">
-        <v>2.8940000000000001</v>
+        <v>-0.247592653589793</v>
       </c>
       <c r="H2" s="3">
         <v>1.365</v>
@@ -3898,7 +3899,7 @@
         <v>1.0924999999999998</v>
       </c>
       <c r="G3" s="3">
-        <v>2.919</v>
+        <v>-0.22259265358979308</v>
       </c>
       <c r="H3" s="3">
         <v>1.4019999999999999</v>
@@ -3924,7 +3925,7 @@
         <v>1.1148</v>
       </c>
       <c r="G4" s="3">
-        <v>2.8980000000000001</v>
+        <v>-0.24359265358979298</v>
       </c>
       <c r="H4" s="3">
         <v>1.405</v>
@@ -3950,7 +3951,7 @@
         <v>1.1184000000000001</v>
       </c>
       <c r="G5" s="3">
-        <v>2.8969999999999998</v>
+        <v>-0.24459265358979332</v>
       </c>
       <c r="H5" s="3">
         <v>1.363</v>
@@ -3976,7 +3977,7 @@
         <v>1.145</v>
       </c>
       <c r="G6" s="3">
-        <v>2.931</v>
+        <v>-0.21059265358979307</v>
       </c>
       <c r="H6" s="3">
         <v>1.407</v>
@@ -4002,7 +4003,7 @@
         <v>1.1674</v>
       </c>
       <c r="G7" s="3">
-        <v>2.9159999999999999</v>
+        <v>-0.2255926535897932</v>
       </c>
       <c r="H7" s="3">
         <v>1.413</v>
@@ -4028,7 +4029,7 @@
         <v>1.1700000000000002</v>
       </c>
       <c r="G8" s="3">
-        <v>2.8969999999999998</v>
+        <v>-0.24459265358979332</v>
       </c>
       <c r="H8" s="3">
         <v>1.361</v>
@@ -4054,7 +4055,7 @@
         <v>1.1988000000000001</v>
       </c>
       <c r="G9" s="3">
-        <v>2.9409999999999998</v>
+        <v>-0.20059265358979328</v>
       </c>
       <c r="H9" s="3">
         <v>1.411</v>
@@ -4080,7 +4081,7 @@
         <v>1.2222</v>
       </c>
       <c r="G10" s="3">
-        <v>2.9329999999999998</v>
+        <v>-0.2085926535897933</v>
       </c>
       <c r="H10" s="3">
         <v>1.421</v>
@@ -4106,7 +4107,7 @@
         <v>1.2222</v>
       </c>
       <c r="G11" s="3">
-        <v>2.8929999999999998</v>
+        <v>-0.24859265358979332</v>
       </c>
       <c r="H11" s="3">
         <v>1.355</v>
@@ -4132,7 +4133,7 @@
         <v>1.2499</v>
       </c>
       <c r="G12" s="3">
-        <v>2.9489999999999998</v>
+        <v>-0.19259265358979327</v>
       </c>
       <c r="H12" s="3">
         <v>1.4139999999999999</v>
@@ -4158,7 +4159,7 @@
         <v>1.2749999999999999</v>
       </c>
       <c r="G13" s="3">
-        <v>2.9470000000000001</v>
+        <v>-0.19459265358979305</v>
       </c>
       <c r="H13" s="3">
         <v>1.427</v>
@@ -4184,7 +4185,7 @@
         <v>1.2734999999999999</v>
       </c>
       <c r="G14" s="3">
-        <v>2.8879999999999999</v>
+        <v>-0.2535926535897932</v>
       </c>
       <c r="H14" s="3">
         <v>1.349</v>
@@ -4210,7 +4211,7 @@
         <v>1.30355</v>
       </c>
       <c r="G15" s="3">
-        <v>2.9550000000000001</v>
+        <v>-0.18659265358979304</v>
       </c>
       <c r="H15" s="3">
         <v>1.4159999999999999</v>
@@ -4236,7 +4237,7 @@
         <v>1.3280000000000001</v>
       </c>
       <c r="G16" s="3">
-        <v>2.9590000000000001</v>
+        <v>-0.18259265358979304</v>
       </c>
       <c r="H16" s="3">
         <v>1.4330000000000001</v>
@@ -4262,7 +4263,7 @@
         <v>1.3360000000000001</v>
       </c>
       <c r="G17" s="3">
-        <v>2.875</v>
+        <v>-0.2665926535897931</v>
       </c>
       <c r="H17" s="3">
         <v>1.34</v>
@@ -4288,7 +4289,7 @@
         <v>1.3562999999999998</v>
       </c>
       <c r="G18" s="3">
-        <v>2.9590000000000001</v>
+        <v>-0.18259265358979304</v>
       </c>
       <c r="H18" s="3">
         <v>1.417</v>
@@ -4314,7 +4315,7 @@
         <v>1.3820999999999999</v>
       </c>
       <c r="G19" s="3">
-        <v>2.968</v>
+        <v>-0.17359265358979314</v>
       </c>
       <c r="H19" s="3">
         <v>1.4370000000000001</v>
@@ -4340,7 +4341,7 @@
         <v>1.4244999999999999</v>
       </c>
       <c r="G20" s="3">
-        <v>2.9209999999999998</v>
+        <v>-0.2205926535897933</v>
       </c>
       <c r="H20" s="3">
         <v>1.4019999999999999</v>
@@ -4366,7 +4367,7 @@
         <v>1.4518925600000001</v>
       </c>
       <c r="G21" s="3">
-        <v>2.8328047600000001</v>
+        <v>-0.30878789358979297</v>
       </c>
       <c r="H21" s="3">
         <v>1.3441136300000001</v>
@@ -4392,7 +4393,7 @@
         <v>1.407</v>
       </c>
       <c r="G22" s="3">
-        <v>2.9620000000000002</v>
+        <v>-0.17959265358979293</v>
       </c>
       <c r="H22" s="3">
         <v>1.417</v>
@@ -4418,7 +4419,7 @@
         <v>1.4346000000000001</v>
       </c>
       <c r="G23" s="3">
-        <v>2.976</v>
+        <v>-0.16559265358979314</v>
       </c>
       <c r="H23" s="3">
         <v>1.44</v>
@@ -4444,7 +4445,7 @@
         <v>1.4578000000000002</v>
       </c>
       <c r="G24" s="3">
-        <v>2.956</v>
+        <v>-0.18559265358979316</v>
       </c>
       <c r="H24" s="3">
         <v>1.4370000000000001</v>
@@ -4470,7 +4471,7 @@
         <v>1.4596500000000001</v>
       </c>
       <c r="G25" s="3">
-        <v>2.9630000000000001</v>
+        <v>-0.17859265358979304</v>
       </c>
       <c r="H25" s="3">
         <v>1.4159999999999999</v>
@@ -4496,7 +4497,7 @@
         <v>1.4896</v>
       </c>
       <c r="G26" s="3">
-        <v>2.9830000000000001</v>
+        <v>-0.15859265358979302</v>
       </c>
       <c r="H26" s="3">
         <v>1.444</v>
@@ -4522,7 +4523,7 @@
         <v>1.51125</v>
       </c>
       <c r="G27" s="3">
-        <v>2.9689999999999999</v>
+        <v>-0.17259265358979325</v>
       </c>
       <c r="H27" s="3">
         <v>1.444</v>
@@ -4548,7 +4549,7 @@
         <v>1.51125</v>
       </c>
       <c r="G28" s="3">
-        <v>2.9620000000000002</v>
+        <v>-0.17959265358979293</v>
       </c>
       <c r="H28" s="3">
         <v>1.413</v>
@@ -4574,7 +4575,7 @@
         <v>1.542</v>
       </c>
       <c r="G29" s="3">
-        <v>2.988</v>
+        <v>-0.15359265358979313</v>
       </c>
       <c r="H29" s="3">
         <v>1.446</v>
@@ -4600,7 +4601,7 @@
         <v>1.5661999999999998</v>
       </c>
       <c r="G30" s="3">
-        <v>2.98</v>
+        <v>-0.16159265358979313</v>
       </c>
       <c r="H30" s="3">
         <v>1.45</v>
@@ -4626,7 +4627,7 @@
         <v>1.5641499999999999</v>
       </c>
       <c r="G31" s="3">
-        <v>2.9569999999999999</v>
+        <v>-0.18459265358979327</v>
       </c>
       <c r="H31" s="3">
         <v>1.4079999999999999</v>
@@ -4652,7 +4653,7 @@
         <v>1.5939000000000001</v>
       </c>
       <c r="G32" s="3">
-        <v>2.9929999999999999</v>
+        <v>-0.14859265358979323</v>
       </c>
       <c r="H32" s="3">
         <v>1.4470000000000001</v>
@@ -4678,7 +4679,7 @@
         <v>1.6189499999999999</v>
       </c>
       <c r="G33" s="3">
-        <v>2.99</v>
+        <v>-0.1515926535897929</v>
       </c>
       <c r="H33" s="3">
         <v>1.456</v>
@@ -4704,7 +4705,7 @@
         <v>1.6146499999999999</v>
       </c>
       <c r="G34" s="3">
-        <v>2.952</v>
+        <v>-0.18959265358979316</v>
       </c>
       <c r="H34" s="3">
         <v>1.4019999999999999</v>
@@ -4730,7 +4731,7 @@
         <v>1.6478000000000002</v>
       </c>
       <c r="G35" s="3">
-        <v>2.9969999999999999</v>
+        <v>-0.14459265358979323</v>
       </c>
       <c r="H35" s="3">
         <v>1.4490000000000001</v>
@@ -4756,7 +4757,7 @@
         <v>1.6739999999999999</v>
       </c>
       <c r="G36" s="3">
-        <v>2.9980000000000002</v>
+        <v>-0.1435926535897929</v>
       </c>
       <c r="H36" s="3">
         <v>1.4590000000000001</v>
@@ -5636,4 +5637,3885 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I121"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>κ</t>
+          </r>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>Confidence level Φ(κ)</t>
+          </r>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>L</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+            </rPr>
+            <t>0,Bar</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color indexed="8"/>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+            </rPr>
+            <t xml:space="preserve"> [cm]</t>
+          </r>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>L</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+            </rPr>
+            <t>0,Y</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color indexed="8"/>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+            </rPr>
+            <t xml:space="preserve"> [cm]</t>
+          </r>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>Configuration type</t>
+          </r>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>Predicted strength [N/m]</t>
+          </r>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>σ</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+            </rPr>
+            <t>cal</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color indexed="8"/>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+            </rPr>
+            <t xml:space="preserve"> strength [N/m]</t>
+          </r>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>Predicted toughness [J/m2]</t>
+          </r>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>σ</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+            </rPr>
+            <t>cal</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color indexed="8"/>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+            </rPr>
+            <t xml:space="preserve"> toughness [J/m2]</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2.12</v>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F2" s="3">
+        <v>102.803</v>
+      </c>
+      <c r="G2" s="3">
+        <v>4.622</v>
+      </c>
+      <c r="H2" s="3">
+        <v>5.109</v>
+      </c>
+      <c r="I2" s="3">
+        <v>2.065</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2.12</v>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F3" s="3">
+        <v>102.552</v>
+      </c>
+      <c r="G3" s="3">
+        <v>4.469</v>
+      </c>
+      <c r="H3" s="3">
+        <v>5.138</v>
+      </c>
+      <c r="I3" s="3">
+        <v>2.224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F4" s="3">
+        <v>102.28</v>
+      </c>
+      <c r="G4" s="3">
+        <v>5.528</v>
+      </c>
+      <c r="H4" s="3">
+        <v>5.413</v>
+      </c>
+      <c r="I4" s="3">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F5" s="3">
+        <v>102.048</v>
+      </c>
+      <c r="G5" s="3">
+        <v>5.762</v>
+      </c>
+      <c r="H5" s="3">
+        <v>5.462</v>
+      </c>
+      <c r="I5" s="3">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F6" s="3">
+        <v>101.594</v>
+      </c>
+      <c r="G6" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>5.562</v>
+      </c>
+      <c r="I6" s="3">
+        <v>2.842</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2.08</v>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F7" s="3">
+        <v>101.46</v>
+      </c>
+      <c r="G7" s="3">
+        <v>7.606</v>
+      </c>
+      <c r="H7" s="3">
+        <v>5.757</v>
+      </c>
+      <c r="I7" s="3">
+        <v>3.108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2.08</v>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F8" s="3">
+        <v>101.074</v>
+      </c>
+      <c r="G8" s="3">
+        <v>7.792</v>
+      </c>
+      <c r="H8" s="3">
+        <v>5.851</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3.176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2.06</v>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F9" s="3">
+        <v>100.742</v>
+      </c>
+      <c r="G9" s="3">
+        <v>8.866</v>
+      </c>
+      <c r="H9" s="3">
+        <v>6.064</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3.321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.06</v>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F10" s="3">
+        <v>100.143</v>
+      </c>
+      <c r="G10" s="3">
+        <v>8.977</v>
+      </c>
+      <c r="H10" s="3">
+        <v>6.241</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3.342</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2.04</v>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F11" s="3">
+        <v>99.913</v>
+      </c>
+      <c r="G11" s="3">
+        <v>9.642</v>
+      </c>
+      <c r="H11" s="3">
+        <v>6.458</v>
+      </c>
+      <c r="I11" s="3">
+        <v>3.386</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2.06</v>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F12" s="3">
+        <v>99.133</v>
+      </c>
+      <c r="G12" s="3">
+        <v>9.1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>6.578</v>
+      </c>
+      <c r="I12" s="3">
+        <v>3.337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2.04</v>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F13" s="3">
+        <v>98.925</v>
+      </c>
+      <c r="G13" s="3">
+        <v>9.744</v>
+      </c>
+      <c r="H13" s="3">
+        <v>6.843</v>
+      </c>
+      <c r="I13" s="3">
+        <v>3.378</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2.02</v>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F14" s="3">
+        <v>98.666</v>
+      </c>
+      <c r="G14" s="3">
+        <v>10.157</v>
+      </c>
+      <c r="H14" s="3">
+        <v>7.182</v>
+      </c>
+      <c r="I14" s="3">
+        <v>3.484</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2.06</v>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F15" s="3">
+        <v>97.448</v>
+      </c>
+      <c r="G15" s="3">
+        <v>9.3</v>
+      </c>
+      <c r="H15" s="3">
+        <v>7.216</v>
+      </c>
+      <c r="I15" s="3">
+        <v>3.302</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2.04</v>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F16" s="3">
+        <v>97.271</v>
+      </c>
+      <c r="G16" s="3">
+        <v>9.933</v>
+      </c>
+      <c r="H16" s="3">
+        <v>7.537</v>
+      </c>
+      <c r="I16" s="3">
+        <v>3.363</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2.02</v>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F17" s="3">
+        <v>96.993</v>
+      </c>
+      <c r="G17" s="3">
+        <v>10.404</v>
+      </c>
+      <c r="H17" s="3">
+        <v>7.94</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3.519</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F18" s="3">
+        <v>96.57</v>
+      </c>
+      <c r="G18" s="3">
+        <v>10.914</v>
+      </c>
+      <c r="H18" s="3">
+        <v>8.412</v>
+      </c>
+      <c r="I18" s="3">
+        <v>3.755</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="D19" s="3">
+        <v>2.04</v>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F19" s="3">
+        <v>94.494</v>
+      </c>
+      <c r="G19" s="3">
+        <v>10.343</v>
+      </c>
+      <c r="H19" s="3">
+        <v>8.74</v>
+      </c>
+      <c r="I19" s="3">
+        <v>3.355</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2.02</v>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F20" s="3">
+        <v>94.233</v>
+      </c>
+      <c r="G20" s="3">
+        <v>10.899</v>
+      </c>
+      <c r="H20" s="3">
+        <v>9.176</v>
+      </c>
+      <c r="I20" s="3">
+        <v>3.555</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F21" s="3">
+        <v>93.759</v>
+      </c>
+      <c r="G21" s="3">
+        <v>11.553</v>
+      </c>
+      <c r="H21" s="3">
+        <v>9.669</v>
+      </c>
+      <c r="I21" s="3">
+        <v>3.797</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1.98</v>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F22" s="3">
+        <v>92.876</v>
+      </c>
+      <c r="G22" s="3">
+        <v>12.519</v>
+      </c>
+      <c r="H22" s="3">
+        <v>10.167</v>
+      </c>
+      <c r="I22" s="3">
+        <v>3.986</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2.04</v>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F23" s="3">
+        <v>89.78</v>
+      </c>
+      <c r="G23" s="3">
+        <v>11.024</v>
+      </c>
+      <c r="H23" s="3">
+        <v>10.696</v>
+      </c>
+      <c r="I23" s="3">
+        <v>3.389</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="D24" s="3">
+        <v>2.02</v>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F24" s="3">
+        <v>89.598</v>
+      </c>
+      <c r="G24" s="3">
+        <v>11.613</v>
+      </c>
+      <c r="H24" s="3">
+        <v>11.107</v>
+      </c>
+      <c r="I24" s="3">
+        <v>3.577</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F25" s="3">
+        <v>89.103</v>
+      </c>
+      <c r="G25" s="3">
+        <v>12.318</v>
+      </c>
+      <c r="H25" s="3">
+        <v>11.568</v>
+      </c>
+      <c r="I25" s="3">
+        <v>3.765</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1.98</v>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F26" s="3">
+        <v>88.07</v>
+      </c>
+      <c r="G26" s="3">
+        <v>13.267</v>
+      </c>
+      <c r="H26" s="3">
+        <v>12.039</v>
+      </c>
+      <c r="I26" s="3">
+        <v>3.873</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B27" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C27" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1.96</v>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F27" s="3">
+        <v>86.365</v>
+      </c>
+      <c r="G27" s="3">
+        <v>14.467</v>
+      </c>
+      <c r="H27" s="3">
+        <v>12.508</v>
+      </c>
+      <c r="I27" s="3">
+        <v>3.881</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B28" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="D28" s="3">
+        <v>2.02</v>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F28" s="3">
+        <v>81.889</v>
+      </c>
+      <c r="G28" s="3">
+        <v>12.003</v>
+      </c>
+      <c r="H28" s="3">
+        <v>13.912</v>
+      </c>
+      <c r="I28" s="3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B29" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="D29" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F29" s="3">
+        <v>81.46</v>
+      </c>
+      <c r="G29" s="3">
+        <v>12.621</v>
+      </c>
+      <c r="H29" s="3">
+        <v>14.281</v>
+      </c>
+      <c r="I29" s="3">
+        <v>3.575</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B30" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1.98</v>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F30" s="3">
+        <v>80.344</v>
+      </c>
+      <c r="G30" s="3">
+        <v>13.428</v>
+      </c>
+      <c r="H30" s="3">
+        <v>14.677</v>
+      </c>
+      <c r="I30" s="3">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B31" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1.48</v>
+      </c>
+      <c r="D31" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F31" s="3">
+        <v>80.124</v>
+      </c>
+      <c r="G31" s="3">
+        <v>5.163</v>
+      </c>
+      <c r="H31" s="3">
+        <v>23.88</v>
+      </c>
+      <c r="I31" s="3">
+        <v>2.571</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="B32" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1.46</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F32" s="3">
+        <v>80.079</v>
+      </c>
+      <c r="G32" s="3">
+        <v>5.427</v>
+      </c>
+      <c r="H32" s="3">
+        <v>24.134</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2.487</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B33" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C33" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="D33" s="3">
+        <v>2.14</v>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F33" s="3">
+        <v>102.406</v>
+      </c>
+      <c r="G33" s="3">
+        <v>4.432</v>
+      </c>
+      <c r="H33" s="3">
+        <v>4.881</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1.789</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B34" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C34" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2.14</v>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F34" s="3">
+        <v>102.538</v>
+      </c>
+      <c r="G34" s="3">
+        <v>4.653</v>
+      </c>
+      <c r="H34" s="3">
+        <v>4.886</v>
+      </c>
+      <c r="I34" s="3">
+        <v>1.727</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B35" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C35" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="D35" s="3">
+        <v>2.14</v>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F35" s="3">
+        <v>102.532</v>
+      </c>
+      <c r="G35" s="3">
+        <v>4.723</v>
+      </c>
+      <c r="H35" s="3">
+        <v>4.911</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1.678</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B36" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C36" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="D36" s="3">
+        <v>2.14</v>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F36" s="3">
+        <v>102.043</v>
+      </c>
+      <c r="G36" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="H36" s="3">
+        <v>4.915</v>
+      </c>
+      <c r="I36" s="3">
+        <v>1.859</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B37" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C37" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D37" s="3">
+        <v>2.14</v>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F37" s="3">
+        <v>102.449</v>
+      </c>
+      <c r="G37" s="3">
+        <v>4.712</v>
+      </c>
+      <c r="H37" s="3">
+        <v>4.945</v>
+      </c>
+      <c r="I37" s="3">
+        <v>1.651</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B38" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C38" s="3">
+        <v>1.14</v>
+      </c>
+      <c r="D38" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F38" s="3">
+        <v>99.496</v>
+      </c>
+      <c r="G38" s="3">
+        <v>2.405</v>
+      </c>
+      <c r="H38" s="3">
+        <v>4.973</v>
+      </c>
+      <c r="I38" s="3">
+        <v>1.672</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B39" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C39" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="D39" s="3">
+        <v>2.22</v>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F39" s="3">
+        <v>98.986</v>
+      </c>
+      <c r="G39" s="3">
+        <v>2.93</v>
+      </c>
+      <c r="H39" s="3">
+        <v>5.036</v>
+      </c>
+      <c r="I39" s="3">
+        <v>1.676</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B40" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C40" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="D40" s="3">
+        <v>2.22</v>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F40" s="3">
+        <v>98.974</v>
+      </c>
+      <c r="G40" s="3">
+        <v>2.82</v>
+      </c>
+      <c r="H40" s="3">
+        <v>5.066</v>
+      </c>
+      <c r="I40" s="3">
+        <v>1.719</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B41" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C41" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="D41" s="3">
+        <v>2.38</v>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F41" s="3">
+        <v>93.221</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1.985</v>
+      </c>
+      <c r="H41" s="3">
+        <v>5.074</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1.306</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B42" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C42" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="D42" s="3">
+        <v>2.22</v>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F42" s="3">
+        <v>98.962</v>
+      </c>
+      <c r="G42" s="3">
+        <v>2.731</v>
+      </c>
+      <c r="H42" s="3">
+        <v>5.076</v>
+      </c>
+      <c r="I42" s="3">
+        <v>1.756</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B43" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="D43" s="3">
+        <v>2.24</v>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F43" s="3">
+        <v>98.126</v>
+      </c>
+      <c r="G43" s="3">
+        <v>2.591</v>
+      </c>
+      <c r="H43" s="3">
+        <v>5.092</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1.672</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B44" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C44" s="3">
+        <v>1.26</v>
+      </c>
+      <c r="D44" s="3">
+        <v>2.38</v>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F44" s="3">
+        <v>93.413</v>
+      </c>
+      <c r="G44" s="3">
+        <v>2.089</v>
+      </c>
+      <c r="H44" s="3">
+        <v>5.099</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1.355</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B45" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C45" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D45" s="3">
+        <v>2.12</v>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F45" s="3">
+        <v>102.803</v>
+      </c>
+      <c r="G45" s="3">
+        <v>4.622</v>
+      </c>
+      <c r="H45" s="3">
+        <v>5.109</v>
+      </c>
+      <c r="I45" s="3">
+        <v>2.065</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B46" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="D46" s="3">
+        <v>2.24</v>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F46" s="3">
+        <v>98.155</v>
+      </c>
+      <c r="G46" s="3">
+        <v>2.498</v>
+      </c>
+      <c r="H46" s="3">
+        <v>5.121</v>
+      </c>
+      <c r="I46" s="3">
+        <v>1.712</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B47" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C47" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="D47" s="3">
+        <v>2.24</v>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F47" s="3">
+        <v>98.183</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2.412</v>
+      </c>
+      <c r="H47" s="3">
+        <v>5.126</v>
+      </c>
+      <c r="I47" s="3">
+        <v>1.742</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B48" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C48" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="D48" s="3">
+        <v>2.26</v>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F48" s="3">
+        <v>97.363</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2.301</v>
+      </c>
+      <c r="H48" s="3">
+        <v>5.151</v>
+      </c>
+      <c r="I48" s="3">
+        <v>1.688</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B49" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C49" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="D49" s="3">
+        <v>2.26</v>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F49" s="3">
+        <v>97.428</v>
+      </c>
+      <c r="G49" s="3">
+        <v>2.199</v>
+      </c>
+      <c r="H49" s="3">
+        <v>5.153</v>
+      </c>
+      <c r="I49" s="3">
+        <v>1.709</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B50" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C50" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="D50" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F50" s="3">
+        <v>92.716</v>
+      </c>
+      <c r="G50" s="3">
+        <v>2.032</v>
+      </c>
+      <c r="H50" s="3">
+        <v>5.172</v>
+      </c>
+      <c r="I50" s="3">
+        <v>1.302</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B51" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C51" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="D51" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F51" s="3">
+        <v>92.936</v>
+      </c>
+      <c r="G51" s="3">
+        <v>2.063</v>
+      </c>
+      <c r="H51" s="3">
+        <v>5.177</v>
+      </c>
+      <c r="I51" s="3">
+        <v>1.339</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B52" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C52" s="3">
+        <v>1.18</v>
+      </c>
+      <c r="D52" s="3">
+        <v>2.18</v>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F52" s="3">
+        <v>96.507</v>
+      </c>
+      <c r="G52" s="3">
+        <v>2.115</v>
+      </c>
+      <c r="H52" s="3">
+        <v>5.237</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1.513</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B53" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C53" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="D53" s="3">
+        <v>2.42</v>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F53" s="3">
+        <v>92.471</v>
+      </c>
+      <c r="G53" s="3">
+        <v>2.083</v>
+      </c>
+      <c r="H53" s="3">
+        <v>5.274</v>
+      </c>
+      <c r="I53" s="3">
+        <v>1.332</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B54" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C54" s="3">
+        <v>1.32</v>
+      </c>
+      <c r="D54" s="3">
+        <v>2.42</v>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F54" s="3">
+        <v>92.22</v>
+      </c>
+      <c r="G54" s="3">
+        <v>2.118</v>
+      </c>
+      <c r="H54" s="3">
+        <v>5.283</v>
+      </c>
+      <c r="I54" s="3">
+        <v>1.317</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B55" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C55" s="3">
+        <v>1.32</v>
+      </c>
+      <c r="D55" s="3">
+        <v>2.44</v>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F55" s="3">
+        <v>92.013</v>
+      </c>
+      <c r="G55" s="3">
+        <v>2.146</v>
+      </c>
+      <c r="H55" s="3">
+        <v>5.385</v>
+      </c>
+      <c r="I55" s="3">
+        <v>1.337</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B56" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1.16</v>
+      </c>
+      <c r="D56" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F56" s="3">
+        <v>97.335</v>
+      </c>
+      <c r="G56" s="3">
+        <v>2.349</v>
+      </c>
+      <c r="H56" s="3">
+        <v>5.536</v>
+      </c>
+      <c r="I56" s="3">
+        <v>1.826</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B57" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C57" s="3">
+        <v>1.18</v>
+      </c>
+      <c r="D57" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F57" s="3">
+        <v>93.542</v>
+      </c>
+      <c r="G57" s="3">
+        <v>3.813</v>
+      </c>
+      <c r="H57" s="3">
+        <v>6.703</v>
+      </c>
+      <c r="I57" s="3">
+        <v>2.202</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B58" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1.14</v>
+      </c>
+      <c r="D58" s="3">
+        <v>2.12</v>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F58" s="3">
+        <v>94.198</v>
+      </c>
+      <c r="G58" s="3">
+        <v>6.64</v>
+      </c>
+      <c r="H58" s="3">
+        <v>7.505</v>
+      </c>
+      <c r="I58" s="3">
+        <v>2.993</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B59" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C59" s="3">
+        <v>1.12</v>
+      </c>
+      <c r="D59" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F59" s="3">
+        <v>94.379</v>
+      </c>
+      <c r="G59" s="3">
+        <v>7.992</v>
+      </c>
+      <c r="H59" s="3">
+        <v>7.816</v>
+      </c>
+      <c r="I59" s="3">
+        <v>3.171</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B60" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="D60" s="3">
+        <v>2.08</v>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F60" s="3">
+        <v>94.556</v>
+      </c>
+      <c r="G60" s="3">
+        <v>8.94</v>
+      </c>
+      <c r="H60" s="3">
+        <v>8.089</v>
+      </c>
+      <c r="I60" s="3">
+        <v>3.221</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B61" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="D61" s="3">
+        <v>2.06</v>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F61" s="3">
+        <v>94.609</v>
+      </c>
+      <c r="G61" s="3">
+        <v>9.697</v>
+      </c>
+      <c r="H61" s="3">
+        <v>8.382</v>
+      </c>
+      <c r="I61" s="3">
+        <v>3.252</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B62" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D62" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F62" s="3">
+        <v>96.57</v>
+      </c>
+      <c r="G62" s="3">
+        <v>10.914</v>
+      </c>
+      <c r="H62" s="3">
+        <v>8.412</v>
+      </c>
+      <c r="I62" s="3">
+        <v>3.755</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B63" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C63" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="D63" s="3">
+        <v>2.04</v>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F63" s="3">
+        <v>94.494</v>
+      </c>
+      <c r="G63" s="3">
+        <v>10.343</v>
+      </c>
+      <c r="H63" s="3">
+        <v>8.74</v>
+      </c>
+      <c r="I63" s="3">
+        <v>3.355</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B64" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="D64" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F64" s="3">
+        <v>87.103</v>
+      </c>
+      <c r="G64" s="3">
+        <v>6.257</v>
+      </c>
+      <c r="H64" s="3">
+        <v>8.837</v>
+      </c>
+      <c r="I64" s="3">
+        <v>2.828</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B65" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C65" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="D65" s="3">
+        <v>2.02</v>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F65" s="3">
+        <v>94.233</v>
+      </c>
+      <c r="G65" s="3">
+        <v>10.899</v>
+      </c>
+      <c r="H65" s="3">
+        <v>9.176</v>
+      </c>
+      <c r="I65" s="3">
+        <v>3.555</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B66" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1.18</v>
+      </c>
+      <c r="D66" s="3">
+        <v>2.14</v>
+      </c>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F66" s="3">
+        <v>87.867</v>
+      </c>
+      <c r="G66" s="3">
+        <v>7.122</v>
+      </c>
+      <c r="H66" s="3">
+        <v>9.226</v>
+      </c>
+      <c r="I66" s="3">
+        <v>3.065</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B67" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1.16</v>
+      </c>
+      <c r="D67" s="3">
+        <v>2.12</v>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F67" s="3">
+        <v>88.494</v>
+      </c>
+      <c r="G67" s="3">
+        <v>8.147</v>
+      </c>
+      <c r="H67" s="3">
+        <v>9.553</v>
+      </c>
+      <c r="I67" s="3">
+        <v>3.207</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B68" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="D68" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F68" s="3">
+        <v>93.759</v>
+      </c>
+      <c r="G68" s="3">
+        <v>11.553</v>
+      </c>
+      <c r="H68" s="3">
+        <v>9.669</v>
+      </c>
+      <c r="I68" s="3">
+        <v>3.797</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B69" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C69" s="3">
+        <v>1.14</v>
+      </c>
+      <c r="D69" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F69" s="3">
+        <v>89.067</v>
+      </c>
+      <c r="G69" s="3">
+        <v>9.004</v>
+      </c>
+      <c r="H69" s="3">
+        <v>9.821</v>
+      </c>
+      <c r="I69" s="3">
+        <v>3.237</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B70" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C70" s="3">
+        <v>1.12</v>
+      </c>
+      <c r="D70" s="3">
+        <v>2.08</v>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F70" s="3">
+        <v>89.517</v>
+      </c>
+      <c r="G70" s="3">
+        <v>9.721</v>
+      </c>
+      <c r="H70" s="3">
+        <v>10.073</v>
+      </c>
+      <c r="I70" s="3">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B71" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C71" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D71" s="3">
+        <v>1.98</v>
+      </c>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F71" s="3">
+        <v>92.876</v>
+      </c>
+      <c r="G71" s="3">
+        <v>12.519</v>
+      </c>
+      <c r="H71" s="3">
+        <v>10.167</v>
+      </c>
+      <c r="I71" s="3">
+        <v>3.986</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B72" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C72" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="D72" s="3">
+        <v>2.06</v>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F72" s="3">
+        <v>89.757</v>
+      </c>
+      <c r="G72" s="3">
+        <v>10.396</v>
+      </c>
+      <c r="H72" s="3">
+        <v>10.355</v>
+      </c>
+      <c r="I72" s="3">
+        <v>3.267</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B73" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C73" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="D73" s="3">
+        <v>2.04</v>
+      </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F73" s="3">
+        <v>89.78</v>
+      </c>
+      <c r="G73" s="3">
+        <v>11.024</v>
+      </c>
+      <c r="H73" s="3">
+        <v>10.696</v>
+      </c>
+      <c r="I73" s="3">
+        <v>3.389</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B74" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C74" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="D74" s="3">
+        <v>2.02</v>
+      </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F74" s="3">
+        <v>89.598</v>
+      </c>
+      <c r="G74" s="3">
+        <v>11.613</v>
+      </c>
+      <c r="H74" s="3">
+        <v>11.107</v>
+      </c>
+      <c r="I74" s="3">
+        <v>3.577</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B75" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C75" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="D75" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F75" s="3">
+        <v>89.103</v>
+      </c>
+      <c r="G75" s="3">
+        <v>12.318</v>
+      </c>
+      <c r="H75" s="3">
+        <v>11.568</v>
+      </c>
+      <c r="I75" s="3">
+        <v>3.765</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B76" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C76" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D76" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F76" s="3">
+        <v>80.102</v>
+      </c>
+      <c r="G76" s="3">
+        <v>4.882</v>
+      </c>
+      <c r="H76" s="3">
+        <v>23.392</v>
+      </c>
+      <c r="I76" s="3">
+        <v>2.544</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B77" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C77" s="3">
+        <v>1.48</v>
+      </c>
+      <c r="D77" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F77" s="3">
+        <v>80.124</v>
+      </c>
+      <c r="G77" s="3">
+        <v>5.163</v>
+      </c>
+      <c r="H77" s="3">
+        <v>23.88</v>
+      </c>
+      <c r="I77" s="3">
+        <v>2.571</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B78" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1.44</v>
+      </c>
+      <c r="D78" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F78" s="3">
+        <v>80.062</v>
+      </c>
+      <c r="G78" s="3">
+        <v>5.454</v>
+      </c>
+      <c r="H78" s="3">
+        <v>24.126</v>
+      </c>
+      <c r="I78" s="3">
+        <v>2.335</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B79" s="3">
+        <v>0.841</v>
+      </c>
+      <c r="C79" s="3">
+        <v>1.46</v>
+      </c>
+      <c r="D79" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F79" s="3">
+        <v>80.079</v>
+      </c>
+      <c r="G79" s="3">
+        <v>5.427</v>
+      </c>
+      <c r="H79" s="3">
+        <v>24.134</v>
+      </c>
+      <c r="I79" s="3">
+        <v>2.487</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B80" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1.16</v>
+      </c>
+      <c r="D80" s="3">
+        <v>2.18</v>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F80" s="3">
+        <v>98.625</v>
+      </c>
+      <c r="G80" s="3">
+        <v>2.3</v>
+      </c>
+      <c r="H80" s="3">
+        <v>4.75</v>
+      </c>
+      <c r="I80" s="3">
+        <v>1.528</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B81" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C81" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="D81" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F81" s="3">
+        <v>101.652</v>
+      </c>
+      <c r="G81" s="3">
+        <v>4.291</v>
+      </c>
+      <c r="H81" s="3">
+        <v>4.868</v>
+      </c>
+      <c r="I81" s="3">
+        <v>1.591</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B82" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C82" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D82" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F82" s="3">
+        <v>101.54</v>
+      </c>
+      <c r="G82" s="3">
+        <v>4.203</v>
+      </c>
+      <c r="H82" s="3">
+        <v>4.907</v>
+      </c>
+      <c r="I82" s="3">
+        <v>1.615</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B83" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C83" s="3">
+        <v>1.14</v>
+      </c>
+      <c r="D83" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F83" s="3">
+        <v>99.496</v>
+      </c>
+      <c r="G83" s="3">
+        <v>2.405</v>
+      </c>
+      <c r="H83" s="3">
+        <v>4.973</v>
+      </c>
+      <c r="I83" s="3">
+        <v>1.672</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B84" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C84" s="3">
+        <v>1.26</v>
+      </c>
+      <c r="D84" s="3">
+        <v>2.36</v>
+      </c>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F84" s="3">
+        <v>93.743</v>
+      </c>
+      <c r="G84" s="3">
+        <v>1.987</v>
+      </c>
+      <c r="H84" s="3">
+        <v>4.995</v>
+      </c>
+      <c r="I84" s="3">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B85" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C85" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="D85" s="3">
+        <v>2.14</v>
+      </c>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F85" s="3">
+        <v>101.311</v>
+      </c>
+      <c r="G85" s="3">
+        <v>3.337</v>
+      </c>
+      <c r="H85" s="3">
+        <v>5.027</v>
+      </c>
+      <c r="I85" s="3">
+        <v>1.949</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B86" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C86" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="D86" s="3">
+        <v>2.22</v>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F86" s="3">
+        <v>98.986</v>
+      </c>
+      <c r="G86" s="3">
+        <v>2.93</v>
+      </c>
+      <c r="H86" s="3">
+        <v>5.036</v>
+      </c>
+      <c r="I86" s="3">
+        <v>1.676</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B87" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C87" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="D87" s="3">
+        <v>2.3</v>
+      </c>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F87" s="3">
+        <v>96.467</v>
+      </c>
+      <c r="G87" s="3">
+        <v>1.767</v>
+      </c>
+      <c r="H87" s="3">
+        <v>5.067</v>
+      </c>
+      <c r="I87" s="3">
+        <v>1.622</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B88" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="D88" s="3">
+        <v>2.38</v>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F88" s="3">
+        <v>93.221</v>
+      </c>
+      <c r="G88" s="3">
+        <v>1.985</v>
+      </c>
+      <c r="H88" s="3">
+        <v>5.074</v>
+      </c>
+      <c r="I88" s="3">
+        <v>1.306</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B89" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C89" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="D89" s="3">
+        <v>2.24</v>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F89" s="3">
+        <v>98.126</v>
+      </c>
+      <c r="G89" s="3">
+        <v>2.591</v>
+      </c>
+      <c r="H89" s="3">
+        <v>5.092</v>
+      </c>
+      <c r="I89" s="3">
+        <v>1.672</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B90" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C90" s="3">
+        <v>1.26</v>
+      </c>
+      <c r="D90" s="3">
+        <v>2.38</v>
+      </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F90" s="3">
+        <v>93.413</v>
+      </c>
+      <c r="G90" s="3">
+        <v>2.089</v>
+      </c>
+      <c r="H90" s="3">
+        <v>5.099</v>
+      </c>
+      <c r="I90" s="3">
+        <v>1.355</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B91" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C91" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="D91" s="3">
+        <v>2.24</v>
+      </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F91" s="3">
+        <v>98.155</v>
+      </c>
+      <c r="G91" s="3">
+        <v>2.498</v>
+      </c>
+      <c r="H91" s="3">
+        <v>5.121</v>
+      </c>
+      <c r="I91" s="3">
+        <v>1.712</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B92" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C92" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="D92" s="3">
+        <v>2.28</v>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F92" s="3">
+        <v>96.89</v>
+      </c>
+      <c r="G92" s="3">
+        <v>1.91</v>
+      </c>
+      <c r="H92" s="3">
+        <v>5.125</v>
+      </c>
+      <c r="I92" s="3">
+        <v>1.678</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B93" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C93" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="D93" s="3">
+        <v>2.24</v>
+      </c>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F93" s="3">
+        <v>98.183</v>
+      </c>
+      <c r="G93" s="3">
+        <v>2.412</v>
+      </c>
+      <c r="H93" s="3">
+        <v>5.126</v>
+      </c>
+      <c r="I93" s="3">
+        <v>1.742</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B94" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C94" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="D94" s="3">
+        <v>2.26</v>
+      </c>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F94" s="3">
+        <v>97.363</v>
+      </c>
+      <c r="G94" s="3">
+        <v>2.301</v>
+      </c>
+      <c r="H94" s="3">
+        <v>5.151</v>
+      </c>
+      <c r="I94" s="3">
+        <v>1.688</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B95" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C95" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="D95" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F95" s="3">
+        <v>92.716</v>
+      </c>
+      <c r="G95" s="3">
+        <v>2.032</v>
+      </c>
+      <c r="H95" s="3">
+        <v>5.172</v>
+      </c>
+      <c r="I95" s="3">
+        <v>1.302</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B96" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C96" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="D96" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F96" s="3">
+        <v>92.936</v>
+      </c>
+      <c r="G96" s="3">
+        <v>2.063</v>
+      </c>
+      <c r="H96" s="3">
+        <v>5.177</v>
+      </c>
+      <c r="I96" s="3">
+        <v>1.339</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B97" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C97" s="3">
+        <v>1.18</v>
+      </c>
+      <c r="D97" s="3">
+        <v>2.18</v>
+      </c>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F97" s="3">
+        <v>96.507</v>
+      </c>
+      <c r="G97" s="3">
+        <v>2.115</v>
+      </c>
+      <c r="H97" s="3">
+        <v>5.237</v>
+      </c>
+      <c r="I97" s="3">
+        <v>1.513</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B98" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C98" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="D98" s="3">
+        <v>2.42</v>
+      </c>
+      <c r="E98" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F98" s="3">
+        <v>92.471</v>
+      </c>
+      <c r="G98" s="3">
+        <v>2.083</v>
+      </c>
+      <c r="H98" s="3">
+        <v>5.274</v>
+      </c>
+      <c r="I98" s="3">
+        <v>1.332</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B99" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C99" s="3">
+        <v>1.32</v>
+      </c>
+      <c r="D99" s="3">
+        <v>2.42</v>
+      </c>
+      <c r="E99" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F99" s="3">
+        <v>92.22</v>
+      </c>
+      <c r="G99" s="3">
+        <v>2.118</v>
+      </c>
+      <c r="H99" s="3">
+        <v>5.283</v>
+      </c>
+      <c r="I99" s="3">
+        <v>1.317</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B100" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C100" s="3">
+        <v>1.32</v>
+      </c>
+      <c r="D100" s="3">
+        <v>2.44</v>
+      </c>
+      <c r="E100" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F100" s="3">
+        <v>92.013</v>
+      </c>
+      <c r="G100" s="3">
+        <v>2.146</v>
+      </c>
+      <c r="H100" s="3">
+        <v>5.385</v>
+      </c>
+      <c r="I100" s="3">
+        <v>1.337</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B101" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C101" s="3">
+        <v>1.34</v>
+      </c>
+      <c r="D101" s="3">
+        <v>2.46</v>
+      </c>
+      <c r="E101" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F101" s="3">
+        <v>91.56</v>
+      </c>
+      <c r="G101" s="3">
+        <v>2.237</v>
+      </c>
+      <c r="H101" s="3">
+        <v>5.504</v>
+      </c>
+      <c r="I101" s="3">
+        <v>1.363</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B102" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C102" s="3">
+        <v>1.16</v>
+      </c>
+      <c r="D102" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="E102" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F102" s="3">
+        <v>97.335</v>
+      </c>
+      <c r="G102" s="3">
+        <v>2.349</v>
+      </c>
+      <c r="H102" s="3">
+        <v>5.536</v>
+      </c>
+      <c r="I102" s="3">
+        <v>1.826</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B103" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C103" s="3">
+        <v>1.36</v>
+      </c>
+      <c r="D103" s="3">
+        <v>2.48</v>
+      </c>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F103" s="3">
+        <v>91.111</v>
+      </c>
+      <c r="G103" s="3">
+        <v>2.343</v>
+      </c>
+      <c r="H103" s="3">
+        <v>5.629</v>
+      </c>
+      <c r="I103" s="3">
+        <v>1.411</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B104" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C104" s="3">
+        <v>1.34</v>
+      </c>
+      <c r="D104" s="3">
+        <v>2.34</v>
+      </c>
+      <c r="E104" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F104" s="3">
+        <v>88.21</v>
+      </c>
+      <c r="G104" s="3">
+        <v>2.803</v>
+      </c>
+      <c r="H104" s="3">
+        <v>5.657</v>
+      </c>
+      <c r="I104" s="3">
+        <v>1.376</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B105" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C105" s="3">
+        <v>1.38</v>
+      </c>
+      <c r="D105" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F105" s="3">
+        <v>90.665</v>
+      </c>
+      <c r="G105" s="3">
+        <v>2.458</v>
+      </c>
+      <c r="H105" s="3">
+        <v>5.756</v>
+      </c>
+      <c r="I105" s="3">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B106" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C106" s="3">
+        <v>1.36</v>
+      </c>
+      <c r="D106" s="3">
+        <v>2.36</v>
+      </c>
+      <c r="E106" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F106" s="3">
+        <v>87.191</v>
+      </c>
+      <c r="G106" s="3">
+        <v>2.766</v>
+      </c>
+      <c r="H106" s="3">
+        <v>5.81</v>
+      </c>
+      <c r="I106" s="3">
+        <v>1.395</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B107" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C107" s="3">
+        <v>1.38</v>
+      </c>
+      <c r="D107" s="3">
+        <v>2.38</v>
+      </c>
+      <c r="E107" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F107" s="3">
+        <v>86.138</v>
+      </c>
+      <c r="G107" s="3">
+        <v>2.701</v>
+      </c>
+      <c r="H107" s="3">
+        <v>5.936</v>
+      </c>
+      <c r="I107" s="3">
+        <v>1.409</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B108" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C108" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="D108" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F108" s="3">
+        <v>85.025</v>
+      </c>
+      <c r="G108" s="3">
+        <v>2.632</v>
+      </c>
+      <c r="H108" s="3">
+        <v>6.03</v>
+      </c>
+      <c r="I108" s="3">
+        <v>1.444</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B109" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C109" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="D109" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="E109" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F109" s="3">
+        <v>87.103</v>
+      </c>
+      <c r="G109" s="3">
+        <v>6.257</v>
+      </c>
+      <c r="H109" s="3">
+        <v>8.837</v>
+      </c>
+      <c r="I109" s="3">
+        <v>2.828</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B110" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C110" s="3">
+        <v>1.16</v>
+      </c>
+      <c r="D110" s="3">
+        <v>2.12</v>
+      </c>
+      <c r="E110" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F110" s="3">
+        <v>88.494</v>
+      </c>
+      <c r="G110" s="3">
+        <v>8.147</v>
+      </c>
+      <c r="H110" s="3">
+        <v>9.553</v>
+      </c>
+      <c r="I110" s="3">
+        <v>3.207</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B111" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C111" s="3">
+        <v>1.14</v>
+      </c>
+      <c r="D111" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="E111" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F111" s="3">
+        <v>89.067</v>
+      </c>
+      <c r="G111" s="3">
+        <v>9.004</v>
+      </c>
+      <c r="H111" s="3">
+        <v>9.821</v>
+      </c>
+      <c r="I111" s="3">
+        <v>3.237</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B112" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C112" s="3">
+        <v>1.12</v>
+      </c>
+      <c r="D112" s="3">
+        <v>2.08</v>
+      </c>
+      <c r="E112" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F112" s="3">
+        <v>89.517</v>
+      </c>
+      <c r="G112" s="3">
+        <v>9.721</v>
+      </c>
+      <c r="H112" s="3">
+        <v>10.073</v>
+      </c>
+      <c r="I112" s="3">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B113" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C113" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="D113" s="3">
+        <v>2.06</v>
+      </c>
+      <c r="E113" s="1" t="inlineStr">
+        <is>
+          <t>Y-dominant</t>
+        </is>
+      </c>
+      <c r="F113" s="3">
+        <v>89.757</v>
+      </c>
+      <c r="G113" s="3">
+        <v>10.396</v>
+      </c>
+      <c r="H113" s="3">
+        <v>10.355</v>
+      </c>
+      <c r="I113" s="3">
+        <v>3.267</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B114" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C114" s="3">
+        <v>1.52</v>
+      </c>
+      <c r="D114" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="E114" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F114" s="3">
+        <v>79.873</v>
+      </c>
+      <c r="G114" s="3">
+        <v>4.707</v>
+      </c>
+      <c r="H114" s="3">
+        <v>22.687</v>
+      </c>
+      <c r="I114" s="3">
+        <v>2.419</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B115" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C115" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D115" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="E115" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F115" s="3">
+        <v>80.102</v>
+      </c>
+      <c r="G115" s="3">
+        <v>4.882</v>
+      </c>
+      <c r="H115" s="3">
+        <v>23.392</v>
+      </c>
+      <c r="I115" s="3">
+        <v>2.544</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B116" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C116" s="3">
+        <v>1.48</v>
+      </c>
+      <c r="D116" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="E116" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F116" s="3">
+        <v>77.433</v>
+      </c>
+      <c r="G116" s="3">
+        <v>4.446</v>
+      </c>
+      <c r="H116" s="3">
+        <v>23.683</v>
+      </c>
+      <c r="I116" s="3">
+        <v>2.035</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B117" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C117" s="3">
+        <v>1.46</v>
+      </c>
+      <c r="D117" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="E117" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F117" s="3">
+        <v>78.398</v>
+      </c>
+      <c r="G117" s="3">
+        <v>4.78</v>
+      </c>
+      <c r="H117" s="3">
+        <v>23.759</v>
+      </c>
+      <c r="I117" s="3">
+        <v>2.097</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B118" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C118" s="3">
+        <v>1.48</v>
+      </c>
+      <c r="D118" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="E118" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F118" s="3">
+        <v>80.124</v>
+      </c>
+      <c r="G118" s="3">
+        <v>5.163</v>
+      </c>
+      <c r="H118" s="3">
+        <v>23.88</v>
+      </c>
+      <c r="I118" s="3">
+        <v>2.571</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B119" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C119" s="3">
+        <v>1.46</v>
+      </c>
+      <c r="D119" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="E119" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F119" s="3">
+        <v>79.273</v>
+      </c>
+      <c r="G119" s="3">
+        <v>5.164</v>
+      </c>
+      <c r="H119" s="3">
+        <v>24.036</v>
+      </c>
+      <c r="I119" s="3">
+        <v>2.276</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B120" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C120" s="3">
+        <v>1.44</v>
+      </c>
+      <c r="D120" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="E120" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F120" s="3">
+        <v>80.062</v>
+      </c>
+      <c r="G120" s="3">
+        <v>5.454</v>
+      </c>
+      <c r="H120" s="3">
+        <v>24.126</v>
+      </c>
+      <c r="I120" s="3">
+        <v>2.335</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" s="1">
+        <v>1.645</v>
+      </c>
+      <c r="B121" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C121" s="3">
+        <v>1.46</v>
+      </c>
+      <c r="D121" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="E121" s="1" t="inlineStr">
+        <is>
+          <t>Bar-dominant</t>
+        </is>
+      </c>
+      <c r="F121" s="3">
+        <v>80.079</v>
+      </c>
+      <c r="G121" s="3">
+        <v>5.427</v>
+      </c>
+      <c r="H121" s="3">
+        <v>24.134</v>
+      </c>
+      <c r="I121" s="3">
+        <v>2.487</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/data/Supplementary Data 4.xlsx
+++ b/data/Supplementary Data 4.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\Research\MEGA\2D_Homo_Binary_Y_Bar\MEGAs\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xinyanyang/Desktop/Manuscripts/6-MEGA/revision/sumbission_files/supp/Supplementary Data File/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2203783E-ADC6-4878-9E9C-0AD4137D839C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A72142-5CE2-8946-8D14-DE95E86403AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1780" yWindow="2300" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="configuration type" sheetId="8" r:id="rId1"/>
     <sheet name="1 Bar-dominant" sheetId="7" r:id="rId2"/>
     <sheet name="2 Balanced" sheetId="5" r:id="rId3"/>
     <sheet name="3 Y-dominant" sheetId="6" r:id="rId4"/>
-    <sheet name="Pareto sets" sheetId="9" r:id="rId8"/>
+    <sheet name="Pareto sets" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="23">
   <si>
     <r>
       <t>L</t>
@@ -290,6 +290,33 @@
   <si>
     <t>Expanded</t>
   </si>
+  <si>
+    <t>κ</t>
+  </si>
+  <si>
+    <t>Confidence level Φ(κ)</t>
+  </si>
+  <si>
+    <t>Configuration type</t>
+  </si>
+  <si>
+    <t>Predicted strength [N/m]</t>
+  </si>
+  <si>
+    <t>Predicted toughness [J/m2]</t>
+  </si>
+  <si>
+    <t>Y-dominant</t>
+  </si>
+  <si>
+    <t>Bar-dominant</t>
+  </si>
+  <si>
+    <t>Calibrated predictive uncertainty of strength [N/m]</t>
+  </si>
+  <si>
+    <t>Calibrated predictive uncertainty of toughness [J/m2]</t>
+  </si>
 </sst>
 </file>
 
@@ -298,7 +325,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -329,6 +356,12 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -413,7 +446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -437,9 +470,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -456,6 +486,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1647,78 +1687,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ADB35C3-BDCF-4088-8382-324DC10B1813}">
   <dimension ref="A1:R19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="17" max="17" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="16" width="8.83203125" style="4"/>
+    <col min="17" max="17" width="25.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="8"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-    </row>
-    <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
-      <c r="C2" s="11">
-        <v>1</v>
-      </c>
-      <c r="D2" s="11">
+      <c r="C2" s="10">
+        <v>1</v>
+      </c>
+      <c r="D2" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="10">
         <v>1.2</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>1.3</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="10">
         <v>1.4</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="10">
         <v>1.5</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>1.6</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="10">
         <v>1.7</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="10">
         <v>1.8</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="10">
         <v>1.9</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="10">
         <v>2</v>
       </c>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-    </row>
-    <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <v>1</v>
       </c>
       <c r="C3" s="8">
@@ -1754,14 +1796,14 @@
       <c r="M3" s="8">
         <v>1</v>
       </c>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-    </row>
-    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="11">
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A4" s="18"/>
+      <c r="B4" s="10">
         <v>1.1000000000000001</v>
       </c>
       <c r="C4" s="8">
@@ -1797,19 +1839,19 @@
       <c r="M4" s="8">
         <v>1</v>
       </c>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="12">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="13" t="s">
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="R4" s="10"/>
-    </row>
-    <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="11">
+      <c r="R4" s="9"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A5" s="18"/>
+      <c r="B5" s="10">
         <v>1.2</v>
       </c>
       <c r="C5" s="8">
@@ -1845,19 +1887,19 @@
       <c r="M5" s="8">
         <v>1</v>
       </c>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="14">
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="13">
         <v>2</v>
       </c>
-      <c r="Q5" s="15" t="s">
+      <c r="Q5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="R5" s="10"/>
-    </row>
-    <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="11">
+      <c r="R5" s="9"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A6" s="18"/>
+      <c r="B6" s="10">
         <v>1.3</v>
       </c>
       <c r="C6" s="8">
@@ -1893,19 +1935,19 @@
       <c r="M6" s="8">
         <v>1</v>
       </c>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="14">
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="13">
         <v>3</v>
       </c>
-      <c r="Q6" s="15" t="s">
+      <c r="Q6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="R6" s="10"/>
-    </row>
-    <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="11">
+      <c r="R6" s="9"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A7" s="18"/>
+      <c r="B7" s="10">
         <v>1.4</v>
       </c>
       <c r="C7" s="8">
@@ -1941,19 +1983,19 @@
       <c r="M7" s="8">
         <v>1</v>
       </c>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="16">
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="15">
         <v>4</v>
       </c>
-      <c r="Q7" s="17" t="s">
+      <c r="Q7" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="R7" s="10"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="11">
+      <c r="R7" s="9"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A8" s="18"/>
+      <c r="B8" s="10">
         <v>1.5</v>
       </c>
       <c r="C8" s="8">
@@ -1989,15 +2031,15 @@
       <c r="M8" s="8">
         <v>1</v>
       </c>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-    </row>
-    <row r="9" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="11">
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A9" s="18"/>
+      <c r="B9" s="10">
         <v>1.6</v>
       </c>
       <c r="C9" s="8">
@@ -2033,14 +2075,14 @@
       <c r="M9" s="8">
         <v>1</v>
       </c>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-    </row>
-    <row r="10" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="11">
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A10" s="18"/>
+      <c r="B10" s="10">
         <v>1.7</v>
       </c>
       <c r="C10" s="8">
@@ -2076,14 +2118,14 @@
       <c r="M10" s="8">
         <v>1</v>
       </c>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-    </row>
-    <row r="11" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="11">
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A11" s="18"/>
+      <c r="B11" s="10">
         <v>1.8</v>
       </c>
       <c r="C11" s="8">
@@ -2119,14 +2161,14 @@
       <c r="M11" s="8">
         <v>1</v>
       </c>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-    </row>
-    <row r="12" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="11">
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A12" s="18"/>
+      <c r="B12" s="10">
         <v>1.9</v>
       </c>
       <c r="C12" s="8">
@@ -2162,14 +2204,14 @@
       <c r="M12" s="8">
         <v>1</v>
       </c>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-    </row>
-    <row r="13" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="11">
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A13" s="18"/>
+      <c r="B13" s="10">
         <v>2</v>
       </c>
       <c r="C13" s="8">
@@ -2205,14 +2247,14 @@
       <c r="M13" s="8">
         <v>4</v>
       </c>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-    </row>
-    <row r="14" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="11">
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A14" s="18"/>
+      <c r="B14" s="10">
         <v>2.1</v>
       </c>
       <c r="C14" s="8">
@@ -2248,14 +2290,14 @@
       <c r="M14" s="8">
         <v>4</v>
       </c>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-    </row>
-    <row r="15" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="11">
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A15" s="18"/>
+      <c r="B15" s="10">
         <v>2.2000000000000002</v>
       </c>
       <c r="C15" s="8">
@@ -2291,14 +2333,14 @@
       <c r="M15" s="8">
         <v>4</v>
       </c>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-    </row>
-    <row r="16" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="11">
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A16" s="18"/>
+      <c r="B16" s="10">
         <v>2.2999999999999998</v>
       </c>
       <c r="C16" s="8">
@@ -2334,14 +2376,14 @@
       <c r="M16" s="8">
         <v>2</v>
       </c>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-    </row>
-    <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="11">
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" s="18"/>
+      <c r="B17" s="10">
         <v>2.4</v>
       </c>
       <c r="C17" s="8">
@@ -2377,14 +2419,14 @@
       <c r="M17" s="8">
         <v>2</v>
       </c>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-    </row>
-    <row r="18" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="11">
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" s="18"/>
+      <c r="B18" s="10">
         <v>2.5</v>
       </c>
       <c r="C18" s="8">
@@ -2420,29 +2462,29 @@
       <c r="M18" s="8">
         <v>2</v>
       </c>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-    </row>
-    <row r="19" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2456,12 +2498,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DD5482D-178F-A644-AC76-FAEC88F12F4F}">
   <dimension ref="A1:H52"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.85546875" style="4"/>
+    <col min="1" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2487,7 +2529,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>1.2</v>
       </c>
@@ -2513,7 +2555,7 @@
         <v>1.8180000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>1.3</v>
       </c>
@@ -2539,7 +2581,7 @@
         <v>1.776</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>1.2990825688073395</v>
       </c>
@@ -2565,7 +2607,7 @@
         <v>1.8080000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>1.4</v>
       </c>
@@ -2591,7 +2633,7 @@
         <v>1.8169999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>1.3986784140969162</v>
       </c>
@@ -2617,7 +2659,7 @@
         <v>1.752</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>1.4018433179723504</v>
       </c>
@@ -2643,7 +2685,7 @@
         <v>1.798</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>1.5</v>
       </c>
@@ -2669,7 +2711,7 @@
         <v>1.871</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>1.4983050847457628</v>
       </c>
@@ -2695,7 +2737,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>1.5000000000000002</v>
       </c>
@@ -2721,7 +2763,7 @@
         <v>1.7410000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>1.4976744186046509</v>
       </c>
@@ -2747,7 +2789,7 @@
         <v>1.786</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>1.4990338164251207</v>
       </c>
@@ -2773,7 +2815,7 @@
         <v>1.7689999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>1.6</v>
       </c>
@@ -2799,7 +2841,7 @@
         <v>1.9330000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>1.5979591836734692</v>
       </c>
@@ -2825,7 +2867,7 @@
         <v>1.776</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>1.5982832618025751</v>
       </c>
@@ -2851,7 +2893,7 @@
         <v>1.804</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>1.5995515695067264</v>
       </c>
@@ -2877,7 +2919,7 @@
         <v>1.7450000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>1.5981308411214954</v>
       </c>
@@ -2903,7 +2945,7 @@
         <v>1.774</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>1.6024154589371979</v>
       </c>
@@ -2929,7 +2971,7 @@
         <v>1.764</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>1.7</v>
       </c>
@@ -2955,7 +2997,7 @@
         <v>1.752</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>1.7019607843137257</v>
       </c>
@@ -2981,7 +3023,7 @@
         <v>1.9119999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>1.7016528925619834</v>
       </c>
@@ -3007,7 +3049,7 @@
         <v>1.758</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>1.7012987012987013</v>
       </c>
@@ -3033,7 +3075,7 @@
         <v>1.798</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>1.6972850678733034</v>
       </c>
@@ -3059,7 +3101,7 @@
         <v>1.7490000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>1.6976525821596244</v>
       </c>
@@ -3085,7 +3127,7 @@
         <v>1.754</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>1.6980582524271846</v>
       </c>
@@ -3111,7 +3153,7 @@
         <v>1.7589999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>1.8</v>
       </c>
@@ -3137,7 +3179,7 @@
         <v>1.7450000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>1.8015151515151517</v>
       </c>
@@ -3163,7 +3205,7 @@
         <v>1.7430000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>1.7999999999999998</v>
       </c>
@@ -3189,7 +3231,7 @@
         <v>1.901</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>1.7974789915966385</v>
       </c>
@@ -3215,7 +3257,7 @@
         <v>1.845</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>1.8026200873362448</v>
       </c>
@@ -3241,7 +3283,7 @@
         <v>1.7949999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>1.7999999999999996</v>
       </c>
@@ -3267,7 +3309,7 @@
         <v>1.752</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>1.7962264150943397</v>
       </c>
@@ -3293,7 +3335,7 @@
         <v>1.7410000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>1.8009708737864079</v>
       </c>
@@ -3319,7 +3361,7 @@
         <v>1.754</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>1.9</v>
       </c>
@@ -3345,7 +3387,7 @@
         <v>1.7350000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>1.9010989010989012</v>
       </c>
@@ -3371,7 +3413,7 @@
         <v>1.7370000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>1.8984496124031007</v>
       </c>
@@ -3397,7 +3439,7 @@
         <v>1.742</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>1.8991869918699189</v>
       </c>
@@ -3423,7 +3465,7 @@
         <v>1.8879999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>1.9016949152542373</v>
       </c>
@@ -3449,7 +3491,7 @@
         <v>1.7490000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>1.902202643171806</v>
       </c>
@@ -3475,7 +3517,7 @@
         <v>1.7889999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>1.9018264840182648</v>
       </c>
@@ -3501,7 +3543,7 @@
         <v>1.7529999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>1.9018867924528304</v>
       </c>
@@ -3527,7 +3569,7 @@
         <v>1.7270000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>1.9038834951456312</v>
       </c>
@@ -3553,7 +3595,7 @@
         <v>1.7490000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>2</v>
       </c>
@@ -3579,7 +3621,7 @@
         <v>1.732</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>2.0007092198581558</v>
       </c>
@@ -3605,7 +3647,7 @@
         <v>1.7250000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>2.0014981273408239</v>
       </c>
@@ -3631,7 +3673,7 @@
         <v>1.728</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>2.0007874015748031</v>
       </c>
@@ -3657,7 +3699,7 @@
         <v>1.732</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>2.0008230452674898</v>
       </c>
@@ -3683,7 +3725,7 @@
         <v>1.7310000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>1.997854077253219</v>
       </c>
@@ -3709,7 +3751,7 @@
         <v>1.8280000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>2</v>
       </c>
@@ -3735,7 +3777,7 @@
         <v>1.7450000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>2.002752293577982</v>
       </c>
@@ -3761,7 +3803,7 @@
         <v>1.7509999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>1.9990521327014217</v>
       </c>
@@ -3787,7 +3829,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>1.9975609756097563</v>
       </c>
@@ -3821,13 +3863,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EF799BD-FC67-534D-96E8-0EF5C2C8D2EC}">
   <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="8" width="10.85546875" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="10.85546875" style="4"/>
+    <col min="1" max="8" width="10.83203125" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3853,7 +3895,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>0.99781420765027318</v>
       </c>
@@ -3873,13 +3915,13 @@
         <v>1.0659000000000001</v>
       </c>
       <c r="G2" s="3">
-        <v>-0.247592653589793</v>
+        <v>-0.24759265358979299</v>
       </c>
       <c r="H2" s="3">
         <v>1.365</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1.0005649717514122</v>
       </c>
@@ -3905,7 +3947,7 @@
         <v>1.4019999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>0.99649122807017532</v>
       </c>
@@ -3931,7 +3973,7 @@
         <v>1.405</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>1.1027027027027025</v>
       </c>
@@ -3957,7 +3999,7 @@
         <v>1.363</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>1.1033519553072626</v>
       </c>
@@ -3983,7 +4025,7 @@
         <v>1.407</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>1.0971098265895955</v>
       </c>
@@ -4003,13 +4045,13 @@
         <v>1.1674</v>
       </c>
       <c r="G7" s="3">
-        <v>-0.2255926535897932</v>
+        <v>-0.22559265358979319</v>
       </c>
       <c r="H7" s="3">
         <v>1.413</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>1.2021505376344086</v>
       </c>
@@ -4035,7 +4077,7 @@
         <v>1.361</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>1.2000000000000002</v>
       </c>
@@ -4061,7 +4103,7 @@
         <v>1.411</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>1.2</v>
       </c>
@@ -4081,13 +4123,13 @@
         <v>1.2222</v>
       </c>
       <c r="G10" s="3">
-        <v>-0.2085926535897933</v>
+        <v>-0.20859265358979329</v>
       </c>
       <c r="H10" s="3">
         <v>1.421</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>1.3026737967914437</v>
       </c>
@@ -4113,7 +4155,7 @@
         <v>1.355</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>1.2977900552486188</v>
       </c>
@@ -4139,7 +4181,7 @@
         <v>1.4139999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>1.2954545454545454</v>
       </c>
@@ -4165,7 +4207,7 @@
         <v>1.427</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>1.3957219251336899</v>
       </c>
@@ -4185,13 +4227,13 @@
         <v>1.2734999999999999</v>
       </c>
       <c r="G14" s="3">
-        <v>-0.2535926535897932</v>
+        <v>-0.25359265358979322</v>
       </c>
       <c r="H14" s="3">
         <v>1.349</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>1.3967032967032968</v>
       </c>
@@ -4217,7 +4259,7 @@
         <v>1.4159999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>1.4022471910112362</v>
       </c>
@@ -4243,7 +4285,7 @@
         <v>1.4330000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>1.4978723404255321</v>
       </c>
@@ -4263,13 +4305,13 @@
         <v>1.3360000000000001</v>
       </c>
       <c r="G17" s="3">
-        <v>-0.2665926535897931</v>
+        <v>-0.26659265358979312</v>
       </c>
       <c r="H17" s="3">
         <v>1.34</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>1.4967213114754097</v>
       </c>
@@ -4295,7 +4337,7 @@
         <v>1.417</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>1.5005586592178772</v>
       </c>
@@ -4321,7 +4363,7 @@
         <v>1.4370000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>1.5</v>
       </c>
@@ -4347,7 +4389,7 @@
         <v>1.4019999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>1.6</v>
       </c>
@@ -4373,7 +4415,7 @@
         <v>1.3441136300000001</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>1.597826086956522</v>
       </c>
@@ -4399,7 +4441,7 @@
         <v>1.417</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>1.6</v>
       </c>
@@ -4425,7 +4467,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>1.5977272727272729</v>
       </c>
@@ -4451,7 +4493,7 @@
         <v>1.4370000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>1.7</v>
       </c>
@@ -4477,7 +4519,7 @@
         <v>1.4159999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>1.7005524861878454</v>
       </c>
@@ -4503,7 +4545,7 @@
         <v>1.444</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>1.6966101694915254</v>
       </c>
@@ -4529,7 +4571,7 @@
         <v>1.444</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>1.8032258064516129</v>
       </c>
@@ -4555,7 +4597,7 @@
         <v>1.413</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>1.8021978021978022</v>
       </c>
@@ -4581,7 +4623,7 @@
         <v>1.446</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>1.7966292134831459</v>
       </c>
@@ -4607,7 +4649,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>1.8956989247311826</v>
       </c>
@@ -4633,7 +4675,7 @@
         <v>1.4079999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>1.9049180327868851</v>
       </c>
@@ -4659,7 +4701,7 @@
         <v>1.4470000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>1.8977653631284916</v>
       </c>
@@ -4685,7 +4727,7 @@
         <v>1.456</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>2.0005347593582887</v>
       </c>
@@ -4711,7 +4753,7 @@
         <v>1.4019999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>1.9956284153005464</v>
       </c>
@@ -4737,7 +4779,7 @@
         <v>1.4490000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>2</v>
       </c>
@@ -4771,12 +4813,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF6E64F7-9C53-C74C-9B87-6FE9DC25B72B}">
   <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.85546875" style="1"/>
+    <col min="1" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4802,7 +4844,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1.0051282051282051</v>
       </c>
@@ -4828,7 +4870,7 @@
         <v>1.7649999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1.0045751633986928</v>
       </c>
@@ -4854,7 +4896,7 @@
         <v>1.7230000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -4880,7 +4922,7 @@
         <v>1.732</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>1.0054054054054054</v>
       </c>
@@ -4906,7 +4948,7 @@
         <v>1.7230000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>0.99310344827586206</v>
       </c>
@@ -4932,7 +4974,7 @@
         <v>1.716</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>0.99230769230769222</v>
       </c>
@@ -4958,7 +5000,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>1.0056338028169014</v>
       </c>
@@ -4984,7 +5026,7 @@
         <v>1.7050000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>1</v>
       </c>
@@ -5010,7 +5052,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>1.0987577639751553</v>
       </c>
@@ -5036,7 +5078,7 @@
         <v>1.7310000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>1.10126582278481</v>
       </c>
@@ -5062,7 +5104,7 @@
         <v>1.7450000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>1.1000000000000001</v>
       </c>
@@ -5088,7 +5130,7 @@
         <v>1.704</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>1.0947368421052632</v>
       </c>
@@ -5114,7 +5156,7 @@
         <v>1.7270000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>1.0999999999999999</v>
       </c>
@@ -5140,7 +5182,7 @@
         <v>1.7170000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>1.1027027027027028</v>
       </c>
@@ -5166,7 +5208,7 @@
         <v>1.7110000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>1.1027397260273974</v>
       </c>
@@ -5192,7 +5234,7 @@
         <v>1.7050000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>1.1000000000000001</v>
       </c>
@@ -5218,7 +5260,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>1.2</v>
       </c>
@@ -5244,7 +5286,7 @@
         <v>1.7370000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>1.1980891719745221</v>
       </c>
@@ -5270,7 +5312,7 @@
         <v>1.7170000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>1.2064516129032259</v>
       </c>
@@ -5296,7 +5338,7 @@
         <v>1.722</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>1.1973684210526316</v>
       </c>
@@ -5322,7 +5364,7 @@
         <v>1.712</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>1.2</v>
       </c>
@@ -5348,7 +5390,7 @@
         <v>1.706</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>1.2</v>
       </c>
@@ -5374,7 +5416,7 @@
         <v>1.7010000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>1.2987421383647801</v>
       </c>
@@ -5400,7 +5442,7 @@
         <v>1.6970000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>1.3070063694267517</v>
       </c>
@@ -5426,7 +5468,7 @@
         <v>1.718</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>1.2974025974025976</v>
       </c>
@@ -5452,7 +5494,7 @@
         <v>1.7070000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>1.3</v>
       </c>
@@ -5478,7 +5520,7 @@
         <v>1.7010000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>1.4018633540372671</v>
       </c>
@@ -5504,7 +5546,7 @@
         <v>1.6859999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>1.3949367088607594</v>
       </c>
@@ -5530,7 +5572,7 @@
         <v>1.716</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>1.4000000000000001</v>
       </c>
@@ -5556,7 +5598,7 @@
         <v>1.7030000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>1.4925925925925922</v>
       </c>
@@ -5582,7 +5624,7 @@
         <v>1.718</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>1.5</v>
       </c>
@@ -5608,7 +5650,7 @@
         <v>1.706</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>1.5999999999999996</v>
       </c>
@@ -5640,196 +5682,80 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I121"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="1" max="1" width="8" style="20" customWidth="1"/>
+    <col min="2" max="2" width="20" style="20" customWidth="1"/>
+    <col min="3" max="4" width="12" style="20" customWidth="1"/>
+    <col min="5" max="5" width="18" style="20" customWidth="1"/>
+    <col min="6" max="7" width="24" style="20" customWidth="1"/>
+    <col min="8" max="9" width="26" style="20" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <r>
-            <t>κ</t>
-          </r>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <r>
-            <t>Confidence level Φ(κ)</t>
-          </r>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <r>
-            <t>L</t>
-          </r>
-          <r>
-            <rPr>
-              <vertAlign val="subscript"/>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Times New Roman"/>
-              <family val="1"/>
-            </rPr>
-            <t>0,Bar</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color indexed="8"/>
-              <rFont val="Times New Roman"/>
-              <family val="1"/>
-            </rPr>
-            <t xml:space="preserve"> [cm]</t>
-          </r>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <r>
-            <t>L</t>
-          </r>
-          <r>
-            <rPr>
-              <vertAlign val="subscript"/>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Times New Roman"/>
-              <family val="1"/>
-            </rPr>
-            <t>0,Y</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color indexed="8"/>
-              <rFont val="Times New Roman"/>
-              <family val="1"/>
-            </rPr>
-            <t xml:space="preserve"> [cm]</t>
-          </r>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <r>
-            <t>Configuration type</t>
-          </r>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <r>
-            <t>Predicted strength [N/m]</t>
-          </r>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <r>
-            <t>σ</t>
-          </r>
-          <r>
-            <rPr>
-              <vertAlign val="subscript"/>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Times New Roman"/>
-              <family val="1"/>
-            </rPr>
-            <t>cal</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color indexed="8"/>
-              <rFont val="Times New Roman"/>
-              <family val="1"/>
-            </rPr>
-            <t xml:space="preserve"> strength [N/m]</t>
-          </r>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <r>
-            <t>Predicted toughness [J/m2]</t>
-          </r>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <r>
-            <t>σ</t>
-          </r>
-          <r>
-            <rPr>
-              <vertAlign val="subscript"/>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Times New Roman"/>
-              <family val="1"/>
-            </rPr>
-            <t>cal</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color indexed="8"/>
-              <rFont val="Times New Roman"/>
-              <family val="1"/>
-            </rPr>
-            <t xml:space="preserve"> toughness [J/m2]</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    <row r="1" spans="1:9" s="19" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B2" s="3">
         <v>0.5</v>
       </c>
       <c r="C2" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3">
         <v>2.12</v>
       </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E2" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F2" s="3">
         <v>102.803</v>
       </c>
       <c r="G2" s="3">
-        <v>4.622</v>
+        <v>4.6219999999999999</v>
       </c>
       <c r="H2" s="3">
         <v>5.109</v>
       </c>
       <c r="I2" s="3">
-        <v>2.065</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>2.0649999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B3" s="3">
         <v>0.5</v>
@@ -5840,58 +5766,54 @@
       <c r="D3" s="3">
         <v>2.12</v>
       </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F3" s="3">
-        <v>102.552</v>
+        <v>102.55200000000001</v>
       </c>
       <c r="G3" s="3">
-        <v>4.469</v>
+        <v>4.4690000000000003</v>
       </c>
       <c r="H3" s="3">
-        <v>5.138</v>
+        <v>5.1379999999999999</v>
       </c>
       <c r="I3" s="3">
-        <v>2.224</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>2.2240000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B4" s="3">
         <v>0.5</v>
       </c>
       <c r="C4" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3">
         <v>2.1</v>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F4" s="3">
         <v>102.28</v>
       </c>
       <c r="G4" s="3">
-        <v>5.528</v>
+        <v>5.5279999999999996</v>
       </c>
       <c r="H4" s="3">
-        <v>5.413</v>
+        <v>5.4130000000000003</v>
       </c>
       <c r="I4" s="3">
         <v>2.65</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B5" s="3">
         <v>0.5</v>
@@ -5902,27 +5824,25 @@
       <c r="D5" s="3">
         <v>2.1</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F5" s="3">
         <v>102.048</v>
       </c>
       <c r="G5" s="3">
-        <v>5.762</v>
+        <v>5.7619999999999996</v>
       </c>
       <c r="H5" s="3">
-        <v>5.462</v>
+        <v>5.4619999999999997</v>
       </c>
       <c r="I5" s="3">
         <v>2.74</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B6" s="3">
         <v>0.5</v>
@@ -5933,58 +5853,54 @@
       <c r="D6" s="3">
         <v>2.1</v>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F6" s="3">
-        <v>101.594</v>
+        <v>101.59399999999999</v>
       </c>
       <c r="G6" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H6" s="3">
-        <v>5.562</v>
+        <v>5.5620000000000003</v>
       </c>
       <c r="I6" s="3">
-        <v>2.842</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>2.8420000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B7" s="3">
         <v>0.5</v>
       </c>
       <c r="C7" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="3">
         <v>2.08</v>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E7" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F7" s="3">
         <v>101.46</v>
       </c>
       <c r="G7" s="3">
-        <v>7.606</v>
+        <v>7.6059999999999999</v>
       </c>
       <c r="H7" s="3">
-        <v>5.757</v>
+        <v>5.7569999999999997</v>
       </c>
       <c r="I7" s="3">
-        <v>3.108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>3.1080000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B8" s="3">
         <v>0.5</v>
@@ -5995,58 +5911,54 @@
       <c r="D8" s="3">
         <v>2.08</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E8" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F8" s="3">
         <v>101.074</v>
       </c>
       <c r="G8" s="3">
-        <v>7.792</v>
+        <v>7.7919999999999998</v>
       </c>
       <c r="H8" s="3">
         <v>5.851</v>
       </c>
       <c r="I8" s="3">
-        <v>3.176</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>3.1760000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B9" s="3">
         <v>0.5</v>
       </c>
       <c r="C9" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3">
         <v>2.06</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E9" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F9" s="3">
         <v>100.742</v>
       </c>
       <c r="G9" s="3">
-        <v>8.866</v>
+        <v>8.8659999999999997</v>
       </c>
       <c r="H9" s="3">
-        <v>6.064</v>
+        <v>6.0640000000000001</v>
       </c>
       <c r="I9" s="3">
-        <v>3.321</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>3.3210000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B10" s="3">
         <v>0.5</v>
@@ -6057,58 +5969,54 @@
       <c r="D10" s="3">
         <v>2.06</v>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E10" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F10" s="3">
         <v>100.143</v>
       </c>
       <c r="G10" s="3">
-        <v>8.977</v>
+        <v>8.9770000000000003</v>
       </c>
       <c r="H10" s="3">
-        <v>6.241</v>
+        <v>6.2409999999999997</v>
       </c>
       <c r="I10" s="3">
-        <v>3.342</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>3.3420000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B11" s="3">
         <v>0.5</v>
       </c>
       <c r="C11" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="3">
         <v>2.04</v>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E11" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F11" s="3">
-        <v>99.913</v>
+        <v>99.912999999999997</v>
       </c>
       <c r="G11" s="3">
-        <v>9.642</v>
+        <v>9.6419999999999995</v>
       </c>
       <c r="H11" s="3">
-        <v>6.458</v>
+        <v>6.4580000000000002</v>
       </c>
       <c r="I11" s="3">
-        <v>3.386</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>3.3860000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B12" s="3">
         <v>0.5</v>
@@ -6119,27 +6027,25 @@
       <c r="D12" s="3">
         <v>2.06</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E12" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F12" s="3">
-        <v>99.133</v>
+        <v>99.132999999999996</v>
       </c>
       <c r="G12" s="3">
         <v>9.1</v>
       </c>
       <c r="H12" s="3">
-        <v>6.578</v>
+        <v>6.5780000000000003</v>
       </c>
       <c r="I12" s="3">
-        <v>3.337</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>3.3370000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B13" s="3">
         <v>0.5</v>
@@ -6150,58 +6056,54 @@
       <c r="D13" s="3">
         <v>2.04</v>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E13" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F13" s="3">
-        <v>98.925</v>
+        <v>98.924999999999997</v>
       </c>
       <c r="G13" s="3">
-        <v>9.744</v>
+        <v>9.7439999999999998</v>
       </c>
       <c r="H13" s="3">
         <v>6.843</v>
       </c>
       <c r="I13" s="3">
-        <v>3.378</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>3.3780000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B14" s="3">
         <v>0.5</v>
       </c>
       <c r="C14" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="3">
         <v>2.02</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E14" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F14" s="3">
-        <v>98.666</v>
+        <v>98.665999999999997</v>
       </c>
       <c r="G14" s="3">
         <v>10.157</v>
       </c>
       <c r="H14" s="3">
-        <v>7.182</v>
+        <v>7.1820000000000004</v>
       </c>
       <c r="I14" s="3">
         <v>3.484</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B15" s="3">
         <v>0.5</v>
@@ -6212,27 +6114,25 @@
       <c r="D15" s="3">
         <v>2.06</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E15" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F15" s="3">
-        <v>97.448</v>
+        <v>97.447999999999993</v>
       </c>
       <c r="G15" s="3">
-        <v>9.3</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="H15" s="3">
-        <v>7.216</v>
+        <v>7.2160000000000002</v>
       </c>
       <c r="I15" s="3">
         <v>3.302</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B16" s="3">
         <v>0.5</v>
@@ -6243,27 +6143,25 @@
       <c r="D16" s="3">
         <v>2.04</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E16" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F16" s="3">
-        <v>97.271</v>
+        <v>97.271000000000001</v>
       </c>
       <c r="G16" s="3">
-        <v>9.933</v>
+        <v>9.9329999999999998</v>
       </c>
       <c r="H16" s="3">
-        <v>7.537</v>
+        <v>7.5369999999999999</v>
       </c>
       <c r="I16" s="3">
         <v>3.363</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B17" s="3">
         <v>0.5</v>
@@ -6274,13 +6172,11 @@
       <c r="D17" s="3">
         <v>2.02</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E17" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F17" s="3">
-        <v>96.993</v>
+        <v>96.992999999999995</v>
       </c>
       <c r="G17" s="3">
         <v>10.404</v>
@@ -6289,26 +6185,24 @@
         <v>7.94</v>
       </c>
       <c r="I17" s="3">
-        <v>3.519</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>3.5190000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B18" s="3">
         <v>0.5</v>
       </c>
       <c r="C18" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F18" s="3">
         <v>96.57</v>
@@ -6317,15 +6211,15 @@
         <v>10.914</v>
       </c>
       <c r="H18" s="3">
-        <v>8.412</v>
+        <v>8.4120000000000008</v>
       </c>
       <c r="I18" s="3">
-        <v>3.755</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>3.7549999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B19" s="3">
         <v>0.5</v>
@@ -6336,10 +6230,8 @@
       <c r="D19" s="3">
         <v>2.04</v>
       </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E19" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F19" s="3">
         <v>94.494</v>
@@ -6354,9 +6246,9 @@
         <v>3.355</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B20" s="3">
         <v>0.5</v>
@@ -6367,27 +6259,25 @@
       <c r="D20" s="3">
         <v>2.02</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E20" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F20" s="3">
-        <v>94.233</v>
+        <v>94.233000000000004</v>
       </c>
       <c r="G20" s="3">
-        <v>10.899</v>
+        <v>10.898999999999999</v>
       </c>
       <c r="H20" s="3">
-        <v>9.176</v>
+        <v>9.1760000000000002</v>
       </c>
       <c r="I20" s="3">
-        <v>3.555</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>3.5550000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B21" s="3">
         <v>0.5</v>
@@ -6396,46 +6286,42 @@
         <v>1.02</v>
       </c>
       <c r="D21" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F21" s="3">
         <v>93.759</v>
       </c>
       <c r="G21" s="3">
-        <v>11.553</v>
+        <v>11.553000000000001</v>
       </c>
       <c r="H21" s="3">
-        <v>9.669</v>
+        <v>9.6690000000000005</v>
       </c>
       <c r="I21" s="3">
-        <v>3.797</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>3.7970000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B22" s="3">
         <v>0.5</v>
       </c>
       <c r="C22" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3">
         <v>1.98</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E22" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F22" s="3">
-        <v>92.876</v>
+        <v>92.876000000000005</v>
       </c>
       <c r="G22" s="3">
         <v>12.519</v>
@@ -6444,12 +6330,12 @@
         <v>10.167</v>
       </c>
       <c r="I22" s="3">
-        <v>3.986</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>3.9860000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B23" s="3">
         <v>0.5</v>
@@ -6460,27 +6346,25 @@
       <c r="D23" s="3">
         <v>2.04</v>
       </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E23" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F23" s="3">
         <v>89.78</v>
       </c>
       <c r="G23" s="3">
-        <v>11.024</v>
+        <v>11.023999999999999</v>
       </c>
       <c r="H23" s="3">
         <v>10.696</v>
       </c>
       <c r="I23" s="3">
-        <v>3.389</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>3.3889999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B24" s="3">
         <v>0.5</v>
@@ -6491,27 +6375,25 @@
       <c r="D24" s="3">
         <v>2.02</v>
       </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E24" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F24" s="3">
-        <v>89.598</v>
+        <v>89.597999999999999</v>
       </c>
       <c r="G24" s="3">
         <v>11.613</v>
       </c>
       <c r="H24" s="3">
-        <v>11.107</v>
+        <v>11.106999999999999</v>
       </c>
       <c r="I24" s="3">
         <v>3.577</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B25" s="3">
         <v>0.5</v>
@@ -6520,15 +6402,13 @@
         <v>1.04</v>
       </c>
       <c r="D25" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F25" s="3">
-        <v>89.103</v>
+        <v>89.102999999999994</v>
       </c>
       <c r="G25" s="3">
         <v>12.318</v>
@@ -6537,12 +6417,12 @@
         <v>11.568</v>
       </c>
       <c r="I25" s="3">
-        <v>3.765</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>3.7650000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B26" s="3">
         <v>0.5</v>
@@ -6553,58 +6433,54 @@
       <c r="D26" s="3">
         <v>1.98</v>
       </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E26" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F26" s="3">
         <v>88.07</v>
       </c>
       <c r="G26" s="3">
-        <v>13.267</v>
+        <v>13.266999999999999</v>
       </c>
       <c r="H26" s="3">
         <v>12.039</v>
       </c>
       <c r="I26" s="3">
-        <v>3.873</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>3.8730000000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B27" s="3">
         <v>0.5</v>
       </c>
       <c r="C27" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="3">
         <v>1.96</v>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E27" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F27" s="3">
-        <v>86.365</v>
+        <v>86.364999999999995</v>
       </c>
       <c r="G27" s="3">
-        <v>14.467</v>
+        <v>14.467000000000001</v>
       </c>
       <c r="H27" s="3">
-        <v>12.508</v>
+        <v>12.507999999999999</v>
       </c>
       <c r="I27" s="3">
-        <v>3.881</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>3.8809999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B28" s="3">
         <v>0.5</v>
@@ -6615,27 +6491,25 @@
       <c r="D28" s="3">
         <v>2.02</v>
       </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E28" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F28" s="3">
-        <v>81.889</v>
+        <v>81.888999999999996</v>
       </c>
       <c r="G28" s="3">
         <v>12.003</v>
       </c>
       <c r="H28" s="3">
-        <v>13.912</v>
+        <v>13.912000000000001</v>
       </c>
       <c r="I28" s="3">
         <v>3.5</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B29" s="3">
         <v>0.5</v>
@@ -6644,29 +6518,27 @@
         <v>1.06</v>
       </c>
       <c r="D29" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F29" s="3">
-        <v>81.46</v>
+        <v>81.459999999999994</v>
       </c>
       <c r="G29" s="3">
         <v>12.621</v>
       </c>
       <c r="H29" s="3">
-        <v>14.281</v>
+        <v>14.281000000000001</v>
       </c>
       <c r="I29" s="3">
-        <v>3.575</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>3.5750000000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B30" s="3">
         <v>0.5</v>
@@ -6677,16 +6549,14 @@
       <c r="D30" s="3">
         <v>1.98</v>
       </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E30" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F30" s="3">
-        <v>80.344</v>
+        <v>80.343999999999994</v>
       </c>
       <c r="G30" s="3">
-        <v>13.428</v>
+        <v>13.428000000000001</v>
       </c>
       <c r="H30" s="3">
         <v>14.677</v>
@@ -6695,9 +6565,9 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B31" s="3">
         <v>0.5</v>
@@ -6706,29 +6576,27 @@
         <v>1.48</v>
       </c>
       <c r="D31" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F31" s="3">
-        <v>80.124</v>
+        <v>80.123999999999995</v>
       </c>
       <c r="G31" s="3">
-        <v>5.163</v>
+        <v>5.1630000000000003</v>
       </c>
       <c r="H31" s="3">
         <v>23.88</v>
       </c>
       <c r="I31" s="3">
-        <v>2.571</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>2.5710000000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B32" s="3">
         <v>0.5</v>
@@ -6737,32 +6605,30 @@
         <v>1.46</v>
       </c>
       <c r="D32" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F32" s="3">
-        <v>80.079</v>
+        <v>80.078999999999994</v>
       </c>
       <c r="G32" s="3">
-        <v>5.427</v>
+        <v>5.4269999999999996</v>
       </c>
       <c r="H32" s="3">
         <v>24.134</v>
       </c>
       <c r="I32" s="3">
-        <v>2.487</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>2.4870000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B33" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C33" s="3">
         <v>1.06</v>
@@ -6770,30 +6636,28 @@
       <c r="D33" s="3">
         <v>2.14</v>
       </c>
-      <c r="E33" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E33" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F33" s="3">
-        <v>102.406</v>
+        <v>102.40600000000001</v>
       </c>
       <c r="G33" s="3">
-        <v>4.432</v>
+        <v>4.4320000000000004</v>
       </c>
       <c r="H33" s="3">
-        <v>4.881</v>
+        <v>4.8810000000000002</v>
       </c>
       <c r="I33" s="3">
-        <v>1.789</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>1.7889999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B34" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C34" s="3">
         <v>1.04</v>
@@ -6801,30 +6665,28 @@
       <c r="D34" s="3">
         <v>2.14</v>
       </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E34" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F34" s="3">
         <v>102.538</v>
       </c>
       <c r="G34" s="3">
-        <v>4.653</v>
+        <v>4.6529999999999996</v>
       </c>
       <c r="H34" s="3">
-        <v>4.886</v>
+        <v>4.8860000000000001</v>
       </c>
       <c r="I34" s="3">
-        <v>1.727</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>1.7270000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B35" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C35" s="3">
         <v>1.02</v>
@@ -6832,30 +6694,28 @@
       <c r="D35" s="3">
         <v>2.14</v>
       </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E35" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F35" s="3">
         <v>102.532</v>
       </c>
       <c r="G35" s="3">
-        <v>4.723</v>
+        <v>4.7229999999999999</v>
       </c>
       <c r="H35" s="3">
-        <v>4.911</v>
+        <v>4.9109999999999996</v>
       </c>
       <c r="I35" s="3">
-        <v>1.678</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>1.6779999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B36" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C36" s="3">
         <v>1.08</v>
@@ -6863,13 +6723,11 @@
       <c r="D36" s="3">
         <v>2.14</v>
       </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E36" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F36" s="3">
-        <v>102.043</v>
+        <v>102.04300000000001</v>
       </c>
       <c r="G36" s="3">
         <v>3.99</v>
@@ -6881,136 +6739,128 @@
         <v>1.859</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B37" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C37" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D37" s="3">
         <v>2.14</v>
       </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E37" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F37" s="3">
         <v>102.449</v>
       </c>
       <c r="G37" s="3">
-        <v>4.712</v>
+        <v>4.7119999999999997</v>
       </c>
       <c r="H37" s="3">
-        <v>4.945</v>
+        <v>4.9450000000000003</v>
       </c>
       <c r="I37" s="3">
         <v>1.651</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B38" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C38" s="3">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="D38" s="3">
         <v>2.16</v>
       </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E38" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F38" s="3">
-        <v>99.496</v>
+        <v>99.495999999999995</v>
       </c>
       <c r="G38" s="3">
-        <v>2.405</v>
+        <v>2.4049999999999998</v>
       </c>
       <c r="H38" s="3">
-        <v>4.973</v>
+        <v>4.9729999999999999</v>
       </c>
       <c r="I38" s="3">
-        <v>1.672</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>1.6719999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B39" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C39" s="3">
         <v>1.08</v>
       </c>
       <c r="D39" s="3">
-        <v>2.22</v>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F39" s="3">
-        <v>98.986</v>
+        <v>98.986000000000004</v>
       </c>
       <c r="G39" s="3">
         <v>2.93</v>
       </c>
       <c r="H39" s="3">
-        <v>5.036</v>
+        <v>5.0359999999999996</v>
       </c>
       <c r="I39" s="3">
-        <v>1.676</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>1.6759999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B40" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C40" s="3">
         <v>1.06</v>
       </c>
       <c r="D40" s="3">
-        <v>2.22</v>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F40" s="3">
-        <v>98.974</v>
+        <v>98.974000000000004</v>
       </c>
       <c r="G40" s="3">
         <v>2.82</v>
       </c>
       <c r="H40" s="3">
-        <v>5.066</v>
+        <v>5.0659999999999998</v>
       </c>
       <c r="I40" s="3">
-        <v>1.719</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>1.7190000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B41" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C41" s="3">
         <v>1.28</v>
@@ -7018,92 +6868,86 @@
       <c r="D41" s="3">
         <v>2.38</v>
       </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E41" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F41" s="3">
-        <v>93.221</v>
+        <v>93.221000000000004</v>
       </c>
       <c r="G41" s="3">
-        <v>1.985</v>
+        <v>1.9850000000000001</v>
       </c>
       <c r="H41" s="3">
-        <v>5.074</v>
+        <v>5.0739999999999998</v>
       </c>
       <c r="I41" s="3">
         <v>1.306</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B42" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C42" s="3">
         <v>1.04</v>
       </c>
       <c r="D42" s="3">
-        <v>2.22</v>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F42" s="3">
-        <v>98.962</v>
+        <v>98.962000000000003</v>
       </c>
       <c r="G42" s="3">
-        <v>2.731</v>
+        <v>2.7309999999999999</v>
       </c>
       <c r="H42" s="3">
-        <v>5.076</v>
+        <v>5.0759999999999996</v>
       </c>
       <c r="I42" s="3">
         <v>1.756</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B43" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C43" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D43" s="3">
-        <v>2.24</v>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F43" s="3">
-        <v>98.126</v>
+        <v>98.126000000000005</v>
       </c>
       <c r="G43" s="3">
-        <v>2.591</v>
+        <v>2.5910000000000002</v>
       </c>
       <c r="H43" s="3">
-        <v>5.092</v>
+        <v>5.0919999999999996</v>
       </c>
       <c r="I43" s="3">
-        <v>1.672</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>1.6719999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B44" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C44" s="3">
         <v>1.26</v>
@@ -7111,185 +6955,173 @@
       <c r="D44" s="3">
         <v>2.38</v>
       </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E44" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F44" s="3">
-        <v>93.413</v>
+        <v>93.412999999999997</v>
       </c>
       <c r="G44" s="3">
         <v>2.089</v>
       </c>
       <c r="H44" s="3">
-        <v>5.099</v>
+        <v>5.0990000000000002</v>
       </c>
       <c r="I44" s="3">
         <v>1.355</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B45" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C45" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D45" s="3">
         <v>2.12</v>
       </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E45" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F45" s="3">
         <v>102.803</v>
       </c>
       <c r="G45" s="3">
-        <v>4.622</v>
+        <v>4.6219999999999999</v>
       </c>
       <c r="H45" s="3">
         <v>5.109</v>
       </c>
       <c r="I45" s="3">
-        <v>2.065</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+        <v>2.0649999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B46" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C46" s="3">
         <v>1.08</v>
       </c>
       <c r="D46" s="3">
-        <v>2.24</v>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F46" s="3">
-        <v>98.155</v>
+        <v>98.155000000000001</v>
       </c>
       <c r="G46" s="3">
-        <v>2.498</v>
+        <v>2.4980000000000002</v>
       </c>
       <c r="H46" s="3">
-        <v>5.121</v>
+        <v>5.1210000000000004</v>
       </c>
       <c r="I46" s="3">
         <v>1.712</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B47" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C47" s="3">
         <v>1.06</v>
       </c>
       <c r="D47" s="3">
-        <v>2.24</v>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F47" s="3">
-        <v>98.183</v>
+        <v>98.183000000000007</v>
       </c>
       <c r="G47" s="3">
-        <v>2.412</v>
+        <v>2.4119999999999999</v>
       </c>
       <c r="H47" s="3">
-        <v>5.126</v>
+        <v>5.1260000000000003</v>
       </c>
       <c r="I47" s="3">
         <v>1.742</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B48" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C48" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D48" s="3">
-        <v>2.26</v>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F48" s="3">
         <v>97.363</v>
       </c>
       <c r="G48" s="3">
-        <v>2.301</v>
+        <v>2.3010000000000002</v>
       </c>
       <c r="H48" s="3">
-        <v>5.151</v>
+        <v>5.1509999999999998</v>
       </c>
       <c r="I48" s="3">
-        <v>1.688</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>1.6879999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B49" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C49" s="3">
         <v>1.08</v>
       </c>
       <c r="D49" s="3">
-        <v>2.26</v>
-      </c>
-      <c r="E49" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F49" s="3">
-        <v>97.428</v>
+        <v>97.427999999999997</v>
       </c>
       <c r="G49" s="3">
-        <v>2.199</v>
+        <v>2.1989999999999998</v>
       </c>
       <c r="H49" s="3">
-        <v>5.153</v>
+        <v>5.1529999999999996</v>
       </c>
       <c r="I49" s="3">
-        <v>1.709</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>1.7090000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B50" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C50" s="3">
         <v>1.3</v>
@@ -7297,30 +7129,28 @@
       <c r="D50" s="3">
         <v>2.4</v>
       </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E50" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F50" s="3">
-        <v>92.716</v>
+        <v>92.715999999999994</v>
       </c>
       <c r="G50" s="3">
         <v>2.032</v>
       </c>
       <c r="H50" s="3">
-        <v>5.172</v>
+        <v>5.1719999999999997</v>
       </c>
       <c r="I50" s="3">
         <v>1.302</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B51" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C51" s="3">
         <v>1.28</v>
@@ -7328,61 +7158,57 @@
       <c r="D51" s="3">
         <v>2.4</v>
       </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E51" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F51" s="3">
-        <v>92.936</v>
+        <v>92.936000000000007</v>
       </c>
       <c r="G51" s="3">
-        <v>2.063</v>
+        <v>2.0630000000000002</v>
       </c>
       <c r="H51" s="3">
-        <v>5.177</v>
+        <v>5.1769999999999996</v>
       </c>
       <c r="I51" s="3">
         <v>1.339</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B52" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C52" s="3">
         <v>1.18</v>
       </c>
       <c r="D52" s="3">
-        <v>2.18</v>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F52" s="3">
-        <v>96.507</v>
+        <v>96.507000000000005</v>
       </c>
       <c r="G52" s="3">
-        <v>2.115</v>
+        <v>2.1150000000000002</v>
       </c>
       <c r="H52" s="3">
-        <v>5.237</v>
+        <v>5.2370000000000001</v>
       </c>
       <c r="I52" s="3">
-        <v>1.513</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+        <v>1.5129999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B53" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C53" s="3">
         <v>1.3</v>
@@ -7390,30 +7216,28 @@
       <c r="D53" s="3">
         <v>2.42</v>
       </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E53" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F53" s="3">
-        <v>92.471</v>
+        <v>92.471000000000004</v>
       </c>
       <c r="G53" s="3">
-        <v>2.083</v>
+        <v>2.0830000000000002</v>
       </c>
       <c r="H53" s="3">
         <v>5.274</v>
       </c>
       <c r="I53" s="3">
-        <v>1.332</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+        <v>1.3320000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B54" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C54" s="3">
         <v>1.32</v>
@@ -7421,30 +7245,28 @@
       <c r="D54" s="3">
         <v>2.42</v>
       </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E54" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F54" s="3">
         <v>92.22</v>
       </c>
       <c r="G54" s="3">
-        <v>2.118</v>
+        <v>2.1179999999999999</v>
       </c>
       <c r="H54" s="3">
-        <v>5.283</v>
+        <v>5.2830000000000004</v>
       </c>
       <c r="I54" s="3">
-        <v>1.317</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
+        <v>1.3169999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B55" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C55" s="3">
         <v>1.32</v>
@@ -7452,61 +7274,57 @@
       <c r="D55" s="3">
         <v>2.44</v>
       </c>
-      <c r="E55" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E55" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F55" s="3">
-        <v>92.013</v>
+        <v>92.013000000000005</v>
       </c>
       <c r="G55" s="3">
-        <v>2.146</v>
+        <v>2.1459999999999999</v>
       </c>
       <c r="H55" s="3">
-        <v>5.385</v>
+        <v>5.3849999999999998</v>
       </c>
       <c r="I55" s="3">
         <v>1.337</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B56" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C56" s="3">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D56" s="3">
         <v>2.16</v>
       </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E56" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F56" s="3">
-        <v>97.335</v>
+        <v>97.334999999999994</v>
       </c>
       <c r="G56" s="3">
-        <v>2.349</v>
+        <v>2.3490000000000002</v>
       </c>
       <c r="H56" s="3">
-        <v>5.536</v>
+        <v>5.5359999999999996</v>
       </c>
       <c r="I56" s="3">
-        <v>1.826</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
+        <v>1.8260000000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B57" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C57" s="3">
         <v>1.18</v>
@@ -7514,123 +7332,115 @@
       <c r="D57" s="3">
         <v>2.16</v>
       </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E57" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F57" s="3">
-        <v>93.542</v>
+        <v>93.542000000000002</v>
       </c>
       <c r="G57" s="3">
-        <v>3.813</v>
+        <v>3.8130000000000002</v>
       </c>
       <c r="H57" s="3">
-        <v>6.703</v>
+        <v>6.7030000000000003</v>
       </c>
       <c r="I57" s="3">
         <v>2.202</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B58" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C58" s="3">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="D58" s="3">
         <v>2.12</v>
       </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E58" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F58" s="3">
-        <v>94.198</v>
+        <v>94.197999999999993</v>
       </c>
       <c r="G58" s="3">
         <v>6.64</v>
       </c>
       <c r="H58" s="3">
-        <v>7.505</v>
+        <v>7.5049999999999999</v>
       </c>
       <c r="I58" s="3">
-        <v>2.993</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
+        <v>2.9929999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B59" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C59" s="3">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="D59" s="3">
         <v>2.1</v>
       </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E59" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F59" s="3">
-        <v>94.379</v>
+        <v>94.379000000000005</v>
       </c>
       <c r="G59" s="3">
         <v>7.992</v>
       </c>
       <c r="H59" s="3">
-        <v>7.816</v>
+        <v>7.8159999999999998</v>
       </c>
       <c r="I59" s="3">
-        <v>3.171</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
+        <v>3.1709999999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B60" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C60" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D60" s="3">
         <v>2.08</v>
       </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E60" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F60" s="3">
-        <v>94.556</v>
+        <v>94.555999999999997</v>
       </c>
       <c r="G60" s="3">
         <v>8.94</v>
       </c>
       <c r="H60" s="3">
-        <v>8.089</v>
+        <v>8.0890000000000004</v>
       </c>
       <c r="I60" s="3">
-        <v>3.221</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+        <v>3.2210000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B61" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C61" s="3">
         <v>1.08</v>
@@ -7638,41 +7448,37 @@
       <c r="D61" s="3">
         <v>2.06</v>
       </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E61" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F61" s="3">
-        <v>94.609</v>
+        <v>94.608999999999995</v>
       </c>
       <c r="G61" s="3">
-        <v>9.697</v>
+        <v>9.6969999999999992</v>
       </c>
       <c r="H61" s="3">
-        <v>8.382</v>
+        <v>8.3819999999999997</v>
       </c>
       <c r="I61" s="3">
-        <v>3.252</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+        <v>3.2519999999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B62" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C62" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D62" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F62" s="3">
         <v>96.57</v>
@@ -7681,18 +7487,18 @@
         <v>10.914</v>
       </c>
       <c r="H62" s="3">
-        <v>8.412</v>
+        <v>8.4120000000000008</v>
       </c>
       <c r="I62" s="3">
-        <v>3.755</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+        <v>3.7549999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B63" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C63" s="3">
         <v>1.06</v>
@@ -7700,10 +7506,8 @@
       <c r="D63" s="3">
         <v>2.04</v>
       </c>
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E63" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F63" s="3">
         <v>94.494</v>
@@ -7718,12 +7522,12 @@
         <v>3.355</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B64" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C64" s="3">
         <v>1.2</v>
@@ -7731,30 +7535,28 @@
       <c r="D64" s="3">
         <v>2.16</v>
       </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E64" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F64" s="3">
-        <v>87.103</v>
+        <v>87.102999999999994</v>
       </c>
       <c r="G64" s="3">
-        <v>6.257</v>
+        <v>6.2569999999999997</v>
       </c>
       <c r="H64" s="3">
-        <v>8.837</v>
+        <v>8.8369999999999997</v>
       </c>
       <c r="I64" s="3">
-        <v>2.828</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
+        <v>2.8279999999999998</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B65" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C65" s="3">
         <v>1.04</v>
@@ -7762,30 +7564,28 @@
       <c r="D65" s="3">
         <v>2.02</v>
       </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E65" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F65" s="3">
-        <v>94.233</v>
+        <v>94.233000000000004</v>
       </c>
       <c r="G65" s="3">
-        <v>10.899</v>
+        <v>10.898999999999999</v>
       </c>
       <c r="H65" s="3">
-        <v>9.176</v>
+        <v>9.1760000000000002</v>
       </c>
       <c r="I65" s="3">
-        <v>3.555</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
+        <v>3.5550000000000002</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B66" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C66" s="3">
         <v>1.18</v>
@@ -7793,140 +7593,130 @@
       <c r="D66" s="3">
         <v>2.14</v>
       </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E66" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F66" s="3">
-        <v>87.867</v>
+        <v>87.867000000000004</v>
       </c>
       <c r="G66" s="3">
-        <v>7.122</v>
+        <v>7.1219999999999999</v>
       </c>
       <c r="H66" s="3">
-        <v>9.226</v>
+        <v>9.2260000000000009</v>
       </c>
       <c r="I66" s="3">
-        <v>3.065</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
+        <v>3.0649999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B67" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C67" s="3">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D67" s="3">
         <v>2.12</v>
       </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E67" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F67" s="3">
         <v>88.494</v>
       </c>
       <c r="G67" s="3">
-        <v>8.147</v>
+        <v>8.1470000000000002</v>
       </c>
       <c r="H67" s="3">
-        <v>9.553</v>
+        <v>9.5530000000000008</v>
       </c>
       <c r="I67" s="3">
-        <v>3.207</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
+        <v>3.2069999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B68" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C68" s="3">
         <v>1.02</v>
       </c>
       <c r="D68" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F68" s="3">
         <v>93.759</v>
       </c>
       <c r="G68" s="3">
-        <v>11.553</v>
+        <v>11.553000000000001</v>
       </c>
       <c r="H68" s="3">
-        <v>9.669</v>
+        <v>9.6690000000000005</v>
       </c>
       <c r="I68" s="3">
-        <v>3.797</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
+        <v>3.7970000000000002</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B69" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C69" s="3">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="D69" s="3">
         <v>2.1</v>
       </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E69" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F69" s="3">
-        <v>89.067</v>
+        <v>89.066999999999993</v>
       </c>
       <c r="G69" s="3">
-        <v>9.004</v>
+        <v>9.0039999999999996</v>
       </c>
       <c r="H69" s="3">
-        <v>9.821</v>
+        <v>9.8209999999999997</v>
       </c>
       <c r="I69" s="3">
-        <v>3.237</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
+        <v>3.2370000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B70" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C70" s="3">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="D70" s="3">
         <v>2.08</v>
       </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E70" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F70" s="3">
-        <v>89.517</v>
+        <v>89.516999999999996</v>
       </c>
       <c r="G70" s="3">
-        <v>9.721</v>
+        <v>9.7210000000000001</v>
       </c>
       <c r="H70" s="3">
         <v>10.073</v>
@@ -7935,26 +7725,24 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B71" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C71" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D71" s="3">
         <v>1.98</v>
       </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E71" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F71" s="3">
-        <v>92.876</v>
+        <v>92.876000000000005</v>
       </c>
       <c r="G71" s="3">
         <v>12.519</v>
@@ -7963,46 +7751,44 @@
         <v>10.167</v>
       </c>
       <c r="I71" s="3">
-        <v>3.986</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
+        <v>3.9860000000000002</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B72" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C72" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D72" s="3">
         <v>2.06</v>
       </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E72" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F72" s="3">
-        <v>89.757</v>
+        <v>89.757000000000005</v>
       </c>
       <c r="G72" s="3">
-        <v>10.396</v>
+        <v>10.396000000000001</v>
       </c>
       <c r="H72" s="3">
         <v>10.355</v>
       </c>
       <c r="I72" s="3">
-        <v>3.267</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
+        <v>3.2669999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B73" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C73" s="3">
         <v>1.08</v>
@@ -8010,30 +7796,28 @@
       <c r="D73" s="3">
         <v>2.04</v>
       </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E73" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F73" s="3">
         <v>89.78</v>
       </c>
       <c r="G73" s="3">
-        <v>11.024</v>
+        <v>11.023999999999999</v>
       </c>
       <c r="H73" s="3">
         <v>10.696</v>
       </c>
       <c r="I73" s="3">
-        <v>3.389</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
+        <v>3.3889999999999998</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B74" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C74" s="3">
         <v>1.06</v>
@@ -8041,44 +7825,40 @@
       <c r="D74" s="3">
         <v>2.02</v>
       </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E74" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F74" s="3">
-        <v>89.598</v>
+        <v>89.597999999999999</v>
       </c>
       <c r="G74" s="3">
         <v>11.613</v>
       </c>
       <c r="H74" s="3">
-        <v>11.107</v>
+        <v>11.106999999999999</v>
       </c>
       <c r="I74" s="3">
         <v>3.577</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B75" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C75" s="3">
         <v>1.04</v>
       </c>
       <c r="D75" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F75" s="3">
-        <v>89.103</v>
+        <v>89.102999999999994</v>
       </c>
       <c r="G75" s="3">
         <v>12.318</v>
@@ -8087,134 +7867,126 @@
         <v>11.568</v>
       </c>
       <c r="I75" s="3">
-        <v>3.765</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
+        <v>3.7650000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B76" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C76" s="3">
         <v>1.5</v>
       </c>
       <c r="D76" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F76" s="3">
-        <v>80.102</v>
+        <v>80.102000000000004</v>
       </c>
       <c r="G76" s="3">
-        <v>4.882</v>
+        <v>4.8819999999999997</v>
       </c>
       <c r="H76" s="3">
-        <v>23.392</v>
+        <v>23.391999999999999</v>
       </c>
       <c r="I76" s="3">
         <v>2.544</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B77" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C77" s="3">
         <v>1.48</v>
       </c>
       <c r="D77" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F77" s="3">
-        <v>80.124</v>
+        <v>80.123999999999995</v>
       </c>
       <c r="G77" s="3">
-        <v>5.163</v>
+        <v>5.1630000000000003</v>
       </c>
       <c r="H77" s="3">
         <v>23.88</v>
       </c>
       <c r="I77" s="3">
-        <v>2.571</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
+        <v>2.5710000000000002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B78" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C78" s="3">
         <v>1.44</v>
       </c>
       <c r="D78" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F78" s="3">
-        <v>80.062</v>
+        <v>80.061999999999998</v>
       </c>
       <c r="G78" s="3">
-        <v>5.454</v>
+        <v>5.4539999999999997</v>
       </c>
       <c r="H78" s="3">
-        <v>24.126</v>
+        <v>24.126000000000001</v>
       </c>
       <c r="I78" s="3">
         <v>2.335</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B79" s="3">
-        <v>0.841</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C79" s="3">
         <v>1.46</v>
       </c>
       <c r="D79" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F79" s="3">
-        <v>80.079</v>
+        <v>80.078999999999994</v>
       </c>
       <c r="G79" s="3">
-        <v>5.427</v>
+        <v>5.4269999999999996</v>
       </c>
       <c r="H79" s="3">
         <v>24.134</v>
       </c>
       <c r="I79" s="3">
-        <v>2.487</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
+        <v>2.4870000000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>1.645</v>
       </c>
@@ -8222,21 +7994,19 @@
         <v>0.95</v>
       </c>
       <c r="C80" s="3">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D80" s="3">
-        <v>2.18</v>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F80" s="3">
         <v>98.625</v>
       </c>
       <c r="G80" s="3">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H80" s="3">
         <v>4.75</v>
@@ -8245,7 +8015,7 @@
         <v>1.528</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>1.645</v>
       </c>
@@ -8258,25 +8028,23 @@
       <c r="D81" s="3">
         <v>2.16</v>
       </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E81" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F81" s="3">
         <v>101.652</v>
       </c>
       <c r="G81" s="3">
-        <v>4.291</v>
+        <v>4.2910000000000004</v>
       </c>
       <c r="H81" s="3">
-        <v>4.868</v>
+        <v>4.8680000000000003</v>
       </c>
       <c r="I81" s="3">
         <v>1.591</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>1.645</v>
       </c>
@@ -8284,21 +8052,19 @@
         <v>0.95</v>
       </c>
       <c r="C82" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D82" s="3">
         <v>2.16</v>
       </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E82" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F82" s="3">
         <v>101.54</v>
       </c>
       <c r="G82" s="3">
-        <v>4.203</v>
+        <v>4.2030000000000003</v>
       </c>
       <c r="H82" s="3">
         <v>4.907</v>
@@ -8307,7 +8073,7 @@
         <v>1.615</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>1.645</v>
       </c>
@@ -8315,30 +8081,28 @@
         <v>0.95</v>
       </c>
       <c r="C83" s="3">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="D83" s="3">
         <v>2.16</v>
       </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E83" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F83" s="3">
-        <v>99.496</v>
+        <v>99.495999999999995</v>
       </c>
       <c r="G83" s="3">
-        <v>2.405</v>
+        <v>2.4049999999999998</v>
       </c>
       <c r="H83" s="3">
-        <v>4.973</v>
+        <v>4.9729999999999999</v>
       </c>
       <c r="I83" s="3">
-        <v>1.672</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
+        <v>1.6719999999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>1.645</v>
       </c>
@@ -8351,25 +8115,23 @@
       <c r="D84" s="3">
         <v>2.36</v>
       </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E84" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F84" s="3">
-        <v>93.743</v>
+        <v>93.742999999999995</v>
       </c>
       <c r="G84" s="3">
-        <v>1.987</v>
+        <v>1.9870000000000001</v>
       </c>
       <c r="H84" s="3">
-        <v>4.995</v>
+        <v>4.9950000000000001</v>
       </c>
       <c r="I84" s="3">
         <v>1.32</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>1.645</v>
       </c>
@@ -8377,30 +8139,28 @@
         <v>0.95</v>
       </c>
       <c r="C85" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D85" s="3">
         <v>2.14</v>
       </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E85" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F85" s="3">
-        <v>101.311</v>
+        <v>101.31100000000001</v>
       </c>
       <c r="G85" s="3">
-        <v>3.337</v>
+        <v>3.3370000000000002</v>
       </c>
       <c r="H85" s="3">
-        <v>5.027</v>
+        <v>5.0270000000000001</v>
       </c>
       <c r="I85" s="3">
-        <v>1.949</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
+        <v>1.9490000000000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>1.645</v>
       </c>
@@ -8411,27 +8171,25 @@
         <v>1.08</v>
       </c>
       <c r="D86" s="3">
-        <v>2.22</v>
-      </c>
-      <c r="E86" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F86" s="3">
-        <v>98.986</v>
+        <v>98.986000000000004</v>
       </c>
       <c r="G86" s="3">
         <v>2.93</v>
       </c>
       <c r="H86" s="3">
-        <v>5.036</v>
+        <v>5.0359999999999996</v>
       </c>
       <c r="I86" s="3">
-        <v>1.676</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
+        <v>1.6759999999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>1.645</v>
       </c>
@@ -8442,27 +8200,25 @@
         <v>1.04</v>
       </c>
       <c r="D87" s="3">
-        <v>2.3</v>
-      </c>
-      <c r="E87" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F87" s="3">
-        <v>96.467</v>
+        <v>96.466999999999999</v>
       </c>
       <c r="G87" s="3">
-        <v>1.767</v>
+        <v>1.7669999999999999</v>
       </c>
       <c r="H87" s="3">
-        <v>5.067</v>
+        <v>5.0670000000000002</v>
       </c>
       <c r="I87" s="3">
-        <v>1.622</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
+        <v>1.6220000000000001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>1.645</v>
       </c>
@@ -8475,25 +8231,23 @@
       <c r="D88" s="3">
         <v>2.38</v>
       </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E88" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F88" s="3">
-        <v>93.221</v>
+        <v>93.221000000000004</v>
       </c>
       <c r="G88" s="3">
-        <v>1.985</v>
+        <v>1.9850000000000001</v>
       </c>
       <c r="H88" s="3">
-        <v>5.074</v>
+        <v>5.0739999999999998</v>
       </c>
       <c r="I88" s="3">
         <v>1.306</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>1.645</v>
       </c>
@@ -8501,30 +8255,28 @@
         <v>0.95</v>
       </c>
       <c r="C89" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D89" s="3">
-        <v>2.24</v>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F89" s="3">
-        <v>98.126</v>
+        <v>98.126000000000005</v>
       </c>
       <c r="G89" s="3">
-        <v>2.591</v>
+        <v>2.5910000000000002</v>
       </c>
       <c r="H89" s="3">
-        <v>5.092</v>
+        <v>5.0919999999999996</v>
       </c>
       <c r="I89" s="3">
-        <v>1.672</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9">
+        <v>1.6719999999999999</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>1.645</v>
       </c>
@@ -8537,25 +8289,23 @@
       <c r="D90" s="3">
         <v>2.38</v>
       </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E90" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F90" s="3">
-        <v>93.413</v>
+        <v>93.412999999999997</v>
       </c>
       <c r="G90" s="3">
         <v>2.089</v>
       </c>
       <c r="H90" s="3">
-        <v>5.099</v>
+        <v>5.0990000000000002</v>
       </c>
       <c r="I90" s="3">
         <v>1.355</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>1.645</v>
       </c>
@@ -8566,27 +8316,25 @@
         <v>1.08</v>
       </c>
       <c r="D91" s="3">
-        <v>2.24</v>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F91" s="3">
-        <v>98.155</v>
+        <v>98.155000000000001</v>
       </c>
       <c r="G91" s="3">
-        <v>2.498</v>
+        <v>2.4980000000000002</v>
       </c>
       <c r="H91" s="3">
-        <v>5.121</v>
+        <v>5.1210000000000004</v>
       </c>
       <c r="I91" s="3">
         <v>1.712</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>1.645</v>
       </c>
@@ -8597,12 +8345,10 @@
         <v>1.06</v>
       </c>
       <c r="D92" s="3">
-        <v>2.28</v>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F92" s="3">
         <v>96.89</v>
@@ -8614,10 +8360,10 @@
         <v>5.125</v>
       </c>
       <c r="I92" s="3">
-        <v>1.678</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9">
+        <v>1.6779999999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>1.645</v>
       </c>
@@ -8628,27 +8374,25 @@
         <v>1.06</v>
       </c>
       <c r="D93" s="3">
-        <v>2.24</v>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F93" s="3">
-        <v>98.183</v>
+        <v>98.183000000000007</v>
       </c>
       <c r="G93" s="3">
-        <v>2.412</v>
+        <v>2.4119999999999999</v>
       </c>
       <c r="H93" s="3">
-        <v>5.126</v>
+        <v>5.1260000000000003</v>
       </c>
       <c r="I93" s="3">
         <v>1.742</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>1.645</v>
       </c>
@@ -8656,30 +8400,28 @@
         <v>0.95</v>
       </c>
       <c r="C94" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D94" s="3">
-        <v>2.26</v>
-      </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F94" s="3">
         <v>97.363</v>
       </c>
       <c r="G94" s="3">
-        <v>2.301</v>
+        <v>2.3010000000000002</v>
       </c>
       <c r="H94" s="3">
-        <v>5.151</v>
+        <v>5.1509999999999998</v>
       </c>
       <c r="I94" s="3">
-        <v>1.688</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9">
+        <v>1.6879999999999999</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>1.645</v>
       </c>
@@ -8692,25 +8434,23 @@
       <c r="D95" s="3">
         <v>2.4</v>
       </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E95" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F95" s="3">
-        <v>92.716</v>
+        <v>92.715999999999994</v>
       </c>
       <c r="G95" s="3">
         <v>2.032</v>
       </c>
       <c r="H95" s="3">
-        <v>5.172</v>
+        <v>5.1719999999999997</v>
       </c>
       <c r="I95" s="3">
         <v>1.302</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>1.645</v>
       </c>
@@ -8723,25 +8463,23 @@
       <c r="D96" s="3">
         <v>2.4</v>
       </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E96" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F96" s="3">
-        <v>92.936</v>
+        <v>92.936000000000007</v>
       </c>
       <c r="G96" s="3">
-        <v>2.063</v>
+        <v>2.0630000000000002</v>
       </c>
       <c r="H96" s="3">
-        <v>5.177</v>
+        <v>5.1769999999999996</v>
       </c>
       <c r="I96" s="3">
         <v>1.339</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>1.645</v>
       </c>
@@ -8752,27 +8490,25 @@
         <v>1.18</v>
       </c>
       <c r="D97" s="3">
-        <v>2.18</v>
-      </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F97" s="3">
-        <v>96.507</v>
+        <v>96.507000000000005</v>
       </c>
       <c r="G97" s="3">
-        <v>2.115</v>
+        <v>2.1150000000000002</v>
       </c>
       <c r="H97" s="3">
-        <v>5.237</v>
+        <v>5.2370000000000001</v>
       </c>
       <c r="I97" s="3">
-        <v>1.513</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9">
+        <v>1.5129999999999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>1.645</v>
       </c>
@@ -8785,25 +8521,23 @@
       <c r="D98" s="3">
         <v>2.42</v>
       </c>
-      <c r="E98" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E98" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F98" s="3">
-        <v>92.471</v>
+        <v>92.471000000000004</v>
       </c>
       <c r="G98" s="3">
-        <v>2.083</v>
+        <v>2.0830000000000002</v>
       </c>
       <c r="H98" s="3">
         <v>5.274</v>
       </c>
       <c r="I98" s="3">
-        <v>1.332</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
+        <v>1.3320000000000001</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>1.645</v>
       </c>
@@ -8816,25 +8550,23 @@
       <c r="D99" s="3">
         <v>2.42</v>
       </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E99" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F99" s="3">
         <v>92.22</v>
       </c>
       <c r="G99" s="3">
-        <v>2.118</v>
+        <v>2.1179999999999999</v>
       </c>
       <c r="H99" s="3">
-        <v>5.283</v>
+        <v>5.2830000000000004</v>
       </c>
       <c r="I99" s="3">
-        <v>1.317</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9">
+        <v>1.3169999999999999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>1.645</v>
       </c>
@@ -8847,25 +8579,23 @@
       <c r="D100" s="3">
         <v>2.44</v>
       </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E100" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F100" s="3">
-        <v>92.013</v>
+        <v>92.013000000000005</v>
       </c>
       <c r="G100" s="3">
-        <v>2.146</v>
+        <v>2.1459999999999999</v>
       </c>
       <c r="H100" s="3">
-        <v>5.385</v>
+        <v>5.3849999999999998</v>
       </c>
       <c r="I100" s="3">
         <v>1.337</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>1.645</v>
       </c>
@@ -8878,25 +8608,23 @@
       <c r="D101" s="3">
         <v>2.46</v>
       </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E101" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F101" s="3">
         <v>91.56</v>
       </c>
       <c r="G101" s="3">
-        <v>2.237</v>
+        <v>2.2370000000000001</v>
       </c>
       <c r="H101" s="3">
-        <v>5.504</v>
+        <v>5.5039999999999996</v>
       </c>
       <c r="I101" s="3">
         <v>1.363</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>1.645</v>
       </c>
@@ -8904,30 +8632,28 @@
         <v>0.95</v>
       </c>
       <c r="C102" s="3">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D102" s="3">
         <v>2.16</v>
       </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E102" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F102" s="3">
-        <v>97.335</v>
+        <v>97.334999999999994</v>
       </c>
       <c r="G102" s="3">
-        <v>2.349</v>
+        <v>2.3490000000000002</v>
       </c>
       <c r="H102" s="3">
-        <v>5.536</v>
+        <v>5.5359999999999996</v>
       </c>
       <c r="I102" s="3">
-        <v>1.826</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9">
+        <v>1.8260000000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>1.645</v>
       </c>
@@ -8940,25 +8666,23 @@
       <c r="D103" s="3">
         <v>2.48</v>
       </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E103" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F103" s="3">
-        <v>91.111</v>
+        <v>91.111000000000004</v>
       </c>
       <c r="G103" s="3">
         <v>2.343</v>
       </c>
       <c r="H103" s="3">
-        <v>5.629</v>
+        <v>5.6289999999999996</v>
       </c>
       <c r="I103" s="3">
         <v>1.411</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>1.645</v>
       </c>
@@ -8971,25 +8695,23 @@
       <c r="D104" s="3">
         <v>2.34</v>
       </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E104" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F104" s="3">
         <v>88.21</v>
       </c>
       <c r="G104" s="3">
-        <v>2.803</v>
+        <v>2.8029999999999999</v>
       </c>
       <c r="H104" s="3">
         <v>5.657</v>
       </c>
       <c r="I104" s="3">
-        <v>1.376</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
+        <v>1.3759999999999999</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>1.645</v>
       </c>
@@ -9002,25 +8724,23 @@
       <c r="D105" s="3">
         <v>2.5</v>
       </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E105" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F105" s="3">
-        <v>90.665</v>
+        <v>90.665000000000006</v>
       </c>
       <c r="G105" s="3">
-        <v>2.458</v>
+        <v>2.4580000000000002</v>
       </c>
       <c r="H105" s="3">
-        <v>5.756</v>
+        <v>5.7560000000000002</v>
       </c>
       <c r="I105" s="3">
         <v>1.48</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>1.645</v>
       </c>
@@ -9033,13 +8753,11 @@
       <c r="D106" s="3">
         <v>2.36</v>
       </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E106" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F106" s="3">
-        <v>87.191</v>
+        <v>87.191000000000003</v>
       </c>
       <c r="G106" s="3">
         <v>2.766</v>
@@ -9051,7 +8769,7 @@
         <v>1.395</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>1.645</v>
       </c>
@@ -9064,25 +8782,23 @@
       <c r="D107" s="3">
         <v>2.38</v>
       </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E107" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F107" s="3">
-        <v>86.138</v>
+        <v>86.138000000000005</v>
       </c>
       <c r="G107" s="3">
-        <v>2.701</v>
+        <v>2.7010000000000001</v>
       </c>
       <c r="H107" s="3">
-        <v>5.936</v>
+        <v>5.9359999999999999</v>
       </c>
       <c r="I107" s="3">
         <v>1.409</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>1.645</v>
       </c>
@@ -9095,16 +8811,14 @@
       <c r="D108" s="3">
         <v>2.4</v>
       </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E108" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F108" s="3">
-        <v>85.025</v>
+        <v>85.025000000000006</v>
       </c>
       <c r="G108" s="3">
-        <v>2.632</v>
+        <v>2.6320000000000001</v>
       </c>
       <c r="H108" s="3">
         <v>6.03</v>
@@ -9113,7 +8827,7 @@
         <v>1.444</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>1.645</v>
       </c>
@@ -9126,25 +8840,23 @@
       <c r="D109" s="3">
         <v>2.16</v>
       </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E109" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F109" s="3">
-        <v>87.103</v>
+        <v>87.102999999999994</v>
       </c>
       <c r="G109" s="3">
-        <v>6.257</v>
+        <v>6.2569999999999997</v>
       </c>
       <c r="H109" s="3">
-        <v>8.837</v>
+        <v>8.8369999999999997</v>
       </c>
       <c r="I109" s="3">
-        <v>2.828</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9">
+        <v>2.8279999999999998</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>1.645</v>
       </c>
@@ -9152,30 +8864,28 @@
         <v>0.95</v>
       </c>
       <c r="C110" s="3">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D110" s="3">
         <v>2.12</v>
       </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E110" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F110" s="3">
         <v>88.494</v>
       </c>
       <c r="G110" s="3">
-        <v>8.147</v>
+        <v>8.1470000000000002</v>
       </c>
       <c r="H110" s="3">
-        <v>9.553</v>
+        <v>9.5530000000000008</v>
       </c>
       <c r="I110" s="3">
-        <v>3.207</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9">
+        <v>3.2069999999999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>1.645</v>
       </c>
@@ -9183,30 +8893,28 @@
         <v>0.95</v>
       </c>
       <c r="C111" s="3">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="D111" s="3">
         <v>2.1</v>
       </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E111" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F111" s="3">
-        <v>89.067</v>
+        <v>89.066999999999993</v>
       </c>
       <c r="G111" s="3">
-        <v>9.004</v>
+        <v>9.0039999999999996</v>
       </c>
       <c r="H111" s="3">
-        <v>9.821</v>
+        <v>9.8209999999999997</v>
       </c>
       <c r="I111" s="3">
-        <v>3.237</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9">
+        <v>3.2370000000000001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>1.645</v>
       </c>
@@ -9214,21 +8922,19 @@
         <v>0.95</v>
       </c>
       <c r="C112" s="3">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="D112" s="3">
         <v>2.08</v>
       </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E112" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F112" s="3">
-        <v>89.517</v>
+        <v>89.516999999999996</v>
       </c>
       <c r="G112" s="3">
-        <v>9.721</v>
+        <v>9.7210000000000001</v>
       </c>
       <c r="H112" s="3">
         <v>10.073</v>
@@ -9237,7 +8943,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>1.645</v>
       </c>
@@ -9245,30 +8951,28 @@
         <v>0.95</v>
       </c>
       <c r="C113" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D113" s="3">
         <v>2.06</v>
       </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>Y-dominant</t>
-        </is>
+      <c r="E113" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F113" s="3">
-        <v>89.757</v>
+        <v>89.757000000000005</v>
       </c>
       <c r="G113" s="3">
-        <v>10.396</v>
+        <v>10.396000000000001</v>
       </c>
       <c r="H113" s="3">
         <v>10.355</v>
       </c>
       <c r="I113" s="3">
-        <v>3.267</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9">
+        <v>3.2669999999999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>1.645</v>
       </c>
@@ -9279,27 +8983,25 @@
         <v>1.52</v>
       </c>
       <c r="D114" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F114" s="3">
-        <v>79.873</v>
+        <v>79.873000000000005</v>
       </c>
       <c r="G114" s="3">
-        <v>4.707</v>
+        <v>4.7069999999999999</v>
       </c>
       <c r="H114" s="3">
-        <v>22.687</v>
+        <v>22.687000000000001</v>
       </c>
       <c r="I114" s="3">
         <v>2.419</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>1.645</v>
       </c>
@@ -9310,27 +9012,25 @@
         <v>1.5</v>
       </c>
       <c r="D115" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F115" s="3">
-        <v>80.102</v>
+        <v>80.102000000000004</v>
       </c>
       <c r="G115" s="3">
-        <v>4.882</v>
+        <v>4.8819999999999997</v>
       </c>
       <c r="H115" s="3">
-        <v>23.392</v>
+        <v>23.391999999999999</v>
       </c>
       <c r="I115" s="3">
         <v>2.544</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>1.645</v>
       </c>
@@ -9343,25 +9043,23 @@
       <c r="D116" s="3">
         <v>1.06</v>
       </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+      <c r="E116" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F116" s="3">
-        <v>77.433</v>
+        <v>77.433000000000007</v>
       </c>
       <c r="G116" s="3">
-        <v>4.446</v>
+        <v>4.4459999999999997</v>
       </c>
       <c r="H116" s="3">
         <v>23.683</v>
       </c>
       <c r="I116" s="3">
-        <v>2.035</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9">
+        <v>2.0350000000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>1.645</v>
       </c>
@@ -9374,13 +9072,11 @@
       <c r="D117" s="3">
         <v>1.04</v>
       </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+      <c r="E117" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F117" s="3">
-        <v>78.398</v>
+        <v>78.397999999999996</v>
       </c>
       <c r="G117" s="3">
         <v>4.78</v>
@@ -9392,7 +9088,7 @@
         <v>2.097</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>1.645</v>
       </c>
@@ -9403,27 +9099,25 @@
         <v>1.48</v>
       </c>
       <c r="D118" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F118" s="3">
-        <v>80.124</v>
+        <v>80.123999999999995</v>
       </c>
       <c r="G118" s="3">
-        <v>5.163</v>
+        <v>5.1630000000000003</v>
       </c>
       <c r="H118" s="3">
         <v>23.88</v>
       </c>
       <c r="I118" s="3">
-        <v>2.571</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9">
+        <v>2.5710000000000002</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>1.645</v>
       </c>
@@ -9436,25 +9130,23 @@
       <c r="D119" s="3">
         <v>1.02</v>
       </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+      <c r="E119" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F119" s="3">
-        <v>79.273</v>
+        <v>79.272999999999996</v>
       </c>
       <c r="G119" s="3">
-        <v>5.164</v>
+        <v>5.1639999999999997</v>
       </c>
       <c r="H119" s="3">
-        <v>24.036</v>
+        <v>24.036000000000001</v>
       </c>
       <c r="I119" s="3">
-        <v>2.276</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9">
+        <v>2.2759999999999998</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>1.645</v>
       </c>
@@ -9465,27 +9157,25 @@
         <v>1.44</v>
       </c>
       <c r="D120" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F120" s="3">
-        <v>80.062</v>
+        <v>80.061999999999998</v>
       </c>
       <c r="G120" s="3">
-        <v>5.454</v>
+        <v>5.4539999999999997</v>
       </c>
       <c r="H120" s="3">
-        <v>24.126</v>
+        <v>24.126000000000001</v>
       </c>
       <c r="I120" s="3">
         <v>2.335</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>1.645</v>
       </c>
@@ -9496,26 +9186,25 @@
         <v>1.46</v>
       </c>
       <c r="D121" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>Bar-dominant</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F121" s="3">
-        <v>80.079</v>
+        <v>80.078999999999994</v>
       </c>
       <c r="G121" s="3">
-        <v>5.427</v>
+        <v>5.4269999999999996</v>
       </c>
       <c r="H121" s="3">
         <v>24.134</v>
       </c>
       <c r="I121" s="3">
-        <v>2.487</v>
+        <v>2.4870000000000001</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>